--- a/research/traditional_assets/database/data/austria/austria_real_estate_general_diversified.xlsx
+++ b/research/traditional_assets/database/data/austria/austria_real_estate_general_diversified.xlsx
@@ -588,124 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.123</v>
-      </c>
-      <c r="E2">
-        <v>-0.0814</v>
+        <v>-0.308</v>
       </c>
       <c r="F2">
-        <v>-0.0075</v>
+        <v>0.174</v>
       </c>
       <c r="G2">
-        <v>0.2027972027972028</v>
+        <v>-0.1368909512761021</v>
       </c>
       <c r="H2">
-        <v>0.2027972027972028</v>
+        <v>-0.1368909512761021</v>
       </c>
       <c r="I2">
-        <v>-0.01200466200466201</v>
+        <v>-0.2088167053364269</v>
       </c>
       <c r="J2">
-        <v>-0.008708398624786584</v>
+        <v>-0.2088167053364269</v>
       </c>
       <c r="K2">
-        <v>21.3</v>
+        <v>-3.65</v>
       </c>
       <c r="L2">
-        <v>0.1241258741258741</v>
+        <v>-0.04234338747099767</v>
       </c>
       <c r="M2">
-        <v>54.2</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="N2">
-        <v>0.2976386600768808</v>
+        <v>0.4222604704532415</v>
       </c>
       <c r="O2">
-        <v>2.544600938967136</v>
+        <v>-20.16438356164383</v>
       </c>
       <c r="P2">
-        <v>26.9</v>
+        <v>17.6</v>
       </c>
       <c r="Q2">
-        <v>0.1477210323997803</v>
+        <v>0.1009753298909925</v>
       </c>
       <c r="R2">
-        <v>1.262910798122066</v>
+        <v>-4.821917808219179</v>
       </c>
       <c r="S2">
-        <v>27.3</v>
+        <v>55.99999999999999</v>
       </c>
       <c r="T2">
-        <v>0.5036900369003691</v>
+        <v>0.7608695652173912</v>
       </c>
       <c r="U2">
-        <v>351.1</v>
+        <v>267.8</v>
       </c>
       <c r="V2">
-        <v>1.928061504667765</v>
+        <v>1.536431440045898</v>
       </c>
       <c r="W2">
-        <v>0.03392259913999045</v>
+        <v>-0.007635983263598326</v>
       </c>
       <c r="X2">
-        <v>0.1975404749044752</v>
+        <v>0.1775595437989929</v>
       </c>
       <c r="Y2">
-        <v>-0.1636178757644848</v>
+        <v>-0.1851955270625912</v>
       </c>
       <c r="Z2">
-        <v>0.1521951219512195</v>
+        <v>0.08935420337928891</v>
       </c>
       <c r="AA2">
-        <v>-0.001325375790699227</v>
+        <v>-0.01865865035762413</v>
       </c>
       <c r="AB2">
-        <v>0.06785234268813402</v>
+        <v>0.05953393831323484</v>
       </c>
       <c r="AC2">
-        <v>-0.06917771847883325</v>
+        <v>-0.07819258867085897</v>
       </c>
       <c r="AD2">
-        <v>837.8</v>
+        <v>935.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>837.8</v>
+        <v>935.4</v>
       </c>
       <c r="AG2">
-        <v>486.6999999999999</v>
+        <v>667.5999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.8214530836356505</v>
+        <v>0.8429305217626385</v>
       </c>
       <c r="AI2">
-        <v>0.6347450564436699</v>
+        <v>0.6791548682204313</v>
       </c>
       <c r="AJ2">
-        <v>0.7277212918660286</v>
+        <v>0.7929682860197174</v>
       </c>
       <c r="AK2">
-        <v>0.5023740710156894</v>
+        <v>0.6017124831004956</v>
       </c>
       <c r="AL2">
-        <v>22.2</v>
+        <v>30.6</v>
       </c>
       <c r="AM2">
-        <v>2.399999999999999</v>
+        <v>-13.1</v>
       </c>
       <c r="AN2">
-        <v>-844.5564516129032</v>
+        <v>-54.7017543859649</v>
       </c>
       <c r="AO2">
-        <v>-0.0927927927927928</v>
+        <v>-0.5882352941176471</v>
       </c>
       <c r="AP2">
-        <v>-490.6249999999999</v>
+        <v>-39.04093567251461</v>
       </c>
       <c r="AQ2">
-        <v>-0.8583333333333338</v>
+        <v>1.374045801526717</v>
       </c>
     </row>
     <row r="3">
@@ -725,124 +722,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.123</v>
-      </c>
-      <c r="E3">
-        <v>-0.0814</v>
+        <v>-0.308</v>
       </c>
       <c r="F3">
-        <v>-0.0075</v>
+        <v>0.174</v>
       </c>
       <c r="G3">
-        <v>0.2027972027972028</v>
+        <v>-0.1368909512761021</v>
       </c>
       <c r="H3">
-        <v>0.2027972027972028</v>
+        <v>-0.1368909512761021</v>
       </c>
       <c r="I3">
-        <v>-0.01200466200466201</v>
+        <v>-0.2088167053364269</v>
       </c>
       <c r="J3">
-        <v>-0.008708398624786584</v>
+        <v>-0.2088167053364269</v>
       </c>
       <c r="K3">
-        <v>21.3</v>
+        <v>-3.65</v>
       </c>
       <c r="L3">
-        <v>0.1241258741258741</v>
+        <v>-0.04234338747099767</v>
       </c>
       <c r="M3">
-        <v>54.2</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="N3">
-        <v>0.2976386600768808</v>
+        <v>0.4222604704532415</v>
       </c>
       <c r="O3">
-        <v>2.544600938967136</v>
+        <v>-20.16438356164383</v>
       </c>
       <c r="P3">
-        <v>26.9</v>
+        <v>17.6</v>
       </c>
       <c r="Q3">
-        <v>0.1477210323997803</v>
+        <v>0.1009753298909925</v>
       </c>
       <c r="R3">
-        <v>1.262910798122066</v>
+        <v>-4.821917808219179</v>
       </c>
       <c r="S3">
-        <v>27.3</v>
+        <v>55.99999999999999</v>
       </c>
       <c r="T3">
-        <v>0.5036900369003691</v>
+        <v>0.7608695652173912</v>
       </c>
       <c r="U3">
-        <v>351.1</v>
+        <v>267.8</v>
       </c>
       <c r="V3">
-        <v>1.928061504667765</v>
+        <v>1.536431440045898</v>
       </c>
       <c r="W3">
-        <v>0.03392259913999045</v>
+        <v>-0.007635983263598326</v>
       </c>
       <c r="X3">
-        <v>0.1975404749044752</v>
+        <v>0.1775595437989929</v>
       </c>
       <c r="Y3">
-        <v>-0.1636178757644848</v>
+        <v>-0.1851955270625912</v>
       </c>
       <c r="Z3">
-        <v>0.1521951219512195</v>
+        <v>0.08935420337928891</v>
       </c>
       <c r="AA3">
-        <v>-0.001325375790699227</v>
+        <v>-0.01865865035762413</v>
       </c>
       <c r="AB3">
-        <v>0.06785234268813402</v>
+        <v>0.05953393831323484</v>
       </c>
       <c r="AC3">
-        <v>-0.06917771847883325</v>
+        <v>-0.07819258867085897</v>
       </c>
       <c r="AD3">
-        <v>837.8</v>
+        <v>935.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>837.8</v>
+        <v>935.4</v>
       </c>
       <c r="AG3">
-        <v>486.6999999999999</v>
+        <v>667.5999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.8214530836356505</v>
+        <v>0.8429305217626385</v>
       </c>
       <c r="AI3">
-        <v>0.6347450564436699</v>
+        <v>0.6791548682204313</v>
       </c>
       <c r="AJ3">
-        <v>0.7277212918660286</v>
+        <v>0.7929682860197174</v>
       </c>
       <c r="AK3">
-        <v>0.5023740710156894</v>
+        <v>0.6017124831004956</v>
       </c>
       <c r="AL3">
-        <v>22.2</v>
+        <v>30.6</v>
       </c>
       <c r="AM3">
-        <v>2.399999999999999</v>
+        <v>-13.1</v>
       </c>
       <c r="AN3">
-        <v>-844.5564516129032</v>
+        <v>-54.7017543859649</v>
       </c>
       <c r="AO3">
-        <v>-0.0927927927927928</v>
+        <v>-0.5882352941176471</v>
       </c>
       <c r="AP3">
-        <v>-490.6249999999999</v>
+        <v>-39.04093567251461</v>
       </c>
       <c r="AQ3">
-        <v>-0.8583333333333338</v>
+        <v>1.374045801526717</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/austria/austria_real_estate_general_diversified.xlsx
+++ b/research/traditional_assets/database/data/austria/austria_real_estate_general_diversified.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07143127575127353</v>
+        <v>0.07130544068947046</v>
       </c>
       <c r="C2">
-        <v>775.5353011414397</v>
+        <v>768.9271005568716</v>
       </c>
       <c r="D2">
-        <v>616.1353011414398</v>
+        <v>619.1751005568716</v>
       </c>
       <c r="E2">
-        <v>-840.3</v>
+        <v>-830.6519999999999</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>9.648</v>
       </c>
       <c r="G2">
         <v>159.4</v>
@@ -1451,45 +1451,45 @@
         <v>5.75</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.4997664</v>
       </c>
       <c r="N2">
-        <v>5.75</v>
+        <v>5.2502336</v>
       </c>
       <c r="O2">
-        <v>1.38</v>
+        <v>1.260056064</v>
       </c>
       <c r="P2">
-        <v>4.37</v>
+        <v>3.990177536</v>
       </c>
       <c r="Q2">
-        <v>7.34</v>
+        <v>6.960177536</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07143127575127353</v>
+        <v>0.07162804110047523</v>
       </c>
       <c r="T2">
-        <v>0.5270060068313374</v>
+        <v>0.5310517095100425</v>
       </c>
       <c r="U2">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V2">
         <v>0.24</v>
       </c>
       <c r="W2">
-        <v>0.038228</v>
+        <v>0.039368</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>11.50537531134546</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07130544068947046</v>
+        <v>0.07123280562766743</v>
       </c>
       <c r="C3">
-        <v>768.9271005568716</v>
+        <v>761.0474395421278</v>
       </c>
       <c r="D3">
-        <v>619.1751005568716</v>
+        <v>620.9434395421279</v>
       </c>
       <c r="E3">
-        <v>-830.6519999999999</v>
+        <v>-821.0039999999999</v>
       </c>
       <c r="F3">
-        <v>9.648</v>
+        <v>19.296</v>
       </c>
       <c r="G3">
         <v>159.4</v>
@@ -1533,45 +1533,45 @@
         <v>5.75</v>
       </c>
       <c r="M3">
-        <v>0.4997664</v>
+        <v>1.0670688</v>
       </c>
       <c r="N3">
-        <v>5.2502336</v>
+        <v>4.682931200000001</v>
       </c>
       <c r="O3">
-        <v>1.260056064</v>
+        <v>1.123903488</v>
       </c>
       <c r="P3">
-        <v>3.990177536</v>
+        <v>3.559027712000001</v>
       </c>
       <c r="Q3">
-        <v>6.960177536</v>
+        <v>6.529027712000001</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07162804110047523</v>
+        <v>0.07182882206904839</v>
       </c>
       <c r="T3">
-        <v>0.5310517095100425</v>
+        <v>0.5351799775495377</v>
       </c>
       <c r="U3">
-        <v>0.0518</v>
+        <v>0.0553</v>
       </c>
       <c r="V3">
         <v>0.24</v>
       </c>
       <c r="W3">
-        <v>0.039368</v>
+        <v>0.042028</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y3">
-        <v>11.50537531134546</v>
+        <v>5.388593500250407</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07123280562766743</v>
+        <v>0.07133421056586436</v>
       </c>
       <c r="C4">
-        <v>761.0474395421278</v>
+        <v>748.9334642989089</v>
       </c>
       <c r="D4">
-        <v>620.9434395421279</v>
+        <v>618.4774642989089</v>
       </c>
       <c r="E4">
-        <v>-821.0039999999999</v>
+        <v>-811.356</v>
       </c>
       <c r="F4">
-        <v>19.296</v>
+        <v>28.944</v>
       </c>
       <c r="G4">
         <v>159.4</v>
@@ -1615,45 +1615,45 @@
         <v>5.75</v>
       </c>
       <c r="M4">
-        <v>1.0670688</v>
+        <v>1.8553104</v>
       </c>
       <c r="N4">
-        <v>4.682931200000001</v>
+        <v>3.8946896</v>
       </c>
       <c r="O4">
-        <v>1.123903488</v>
+        <v>0.934725504</v>
       </c>
       <c r="P4">
-        <v>3.559027712000001</v>
+        <v>2.959964096</v>
       </c>
       <c r="Q4">
-        <v>6.529027712000001</v>
+        <v>5.929964096000001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07182882206904839</v>
+        <v>0.07203374285140657</v>
       </c>
       <c r="T4">
-        <v>0.5351799775495377</v>
+        <v>0.5393933645176823</v>
       </c>
       <c r="U4">
-        <v>0.0553</v>
+        <v>0.0641</v>
       </c>
       <c r="V4">
         <v>0.24</v>
       </c>
       <c r="W4">
-        <v>0.042028</v>
+        <v>0.048716</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y4">
-        <v>5.388593500250407</v>
+        <v>3.099211862338507</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07133421056586436</v>
+        <v>0.0720892155040613</v>
       </c>
       <c r="C5">
-        <v>748.9334642989089</v>
+        <v>721.5232933570998</v>
       </c>
       <c r="D5">
-        <v>618.4774642989089</v>
+        <v>600.7152933570998</v>
       </c>
       <c r="E5">
-        <v>-811.356</v>
+        <v>-801.708</v>
       </c>
       <c r="F5">
-        <v>28.944</v>
+        <v>38.592</v>
       </c>
       <c r="G5">
         <v>159.4</v>
@@ -1697,45 +1697,45 @@
         <v>5.75</v>
       </c>
       <c r="M5">
-        <v>1.8553104</v>
+        <v>3.47328</v>
       </c>
       <c r="N5">
-        <v>3.8946896</v>
+        <v>2.27672</v>
       </c>
       <c r="O5">
-        <v>0.934725504</v>
+        <v>0.5464128</v>
       </c>
       <c r="P5">
-        <v>2.959964096</v>
+        <v>1.7303072</v>
       </c>
       <c r="Q5">
-        <v>5.929964096000001</v>
+        <v>4.7003072</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07203374285140657</v>
+        <v>0.07224293281673053</v>
       </c>
       <c r="T5">
-        <v>0.5393933645176823</v>
+        <v>0.5436945303809964</v>
       </c>
       <c r="U5">
-        <v>0.0641</v>
+        <v>0.09</v>
       </c>
       <c r="V5">
         <v>0.24</v>
       </c>
       <c r="W5">
-        <v>0.048716</v>
+        <v>0.0684</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y5">
-        <v>3.099211862338507</v>
+        <v>1.655495669799152</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.0720892155040613</v>
+        <v>0.07480118872799445</v>
       </c>
       <c r="C6">
-        <v>721.5232933570998</v>
+        <v>655.700913538695</v>
       </c>
       <c r="D6">
-        <v>600.7152933570998</v>
+        <v>544.540913538695</v>
       </c>
       <c r="E6">
-        <v>-801.708</v>
+        <v>-792.0599999999999</v>
       </c>
       <c r="F6">
-        <v>38.592</v>
+        <v>48.24</v>
       </c>
       <c r="G6">
         <v>159.4</v>
@@ -1779,45 +1779,45 @@
         <v>5.75</v>
       </c>
       <c r="M6">
-        <v>3.47328</v>
+        <v>7.081632000000001</v>
       </c>
       <c r="N6">
-        <v>2.27672</v>
+        <v>-1.331632000000001</v>
       </c>
       <c r="O6">
-        <v>0.5464128</v>
+        <v>-0.3195916800000002</v>
       </c>
       <c r="P6">
-        <v>1.7303072</v>
+        <v>-1.012040320000001</v>
       </c>
       <c r="Q6">
-        <v>4.7003072</v>
+        <v>1.95795968</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07224293281673053</v>
+        <v>0.07251740735442203</v>
       </c>
       <c r="T6">
-        <v>0.5436945303809964</v>
+        <v>0.5493380157653899</v>
       </c>
       <c r="U6">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V6">
-        <v>0.24</v>
+        <v>0.1948703349736332</v>
       </c>
       <c r="W6">
-        <v>0.0684</v>
+        <v>0.1181930348258707</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y6">
-        <v>1.655495669799152</v>
+        <v>0.8119597290568049</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07480118872799445</v>
+        <v>0.08124544975448708</v>
       </c>
       <c r="C7">
-        <v>655.700913538695</v>
+        <v>547.0511005907896</v>
       </c>
       <c r="D7">
-        <v>544.540913538695</v>
+        <v>445.5391005907896</v>
       </c>
       <c r="E7">
-        <v>-792.0599999999999</v>
+        <v>-782.4119999999999</v>
       </c>
       <c r="F7">
-        <v>48.24</v>
+        <v>57.88800000000001</v>
       </c>
       <c r="G7">
         <v>159.4</v>
@@ -1861,45 +1861,45 @@
         <v>5.75</v>
       </c>
       <c r="M7">
-        <v>7.081632000000001</v>
+        <v>13.6499904</v>
       </c>
       <c r="N7">
-        <v>-1.331632000000001</v>
+        <v>-7.899990400000002</v>
       </c>
       <c r="O7">
-        <v>-0.3195916800000002</v>
+        <v>-1.895997696</v>
       </c>
       <c r="P7">
-        <v>-1.012040320000001</v>
+        <v>-6.003992704000002</v>
       </c>
       <c r="Q7">
-        <v>1.95795968</v>
+        <v>-3.033992704000001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07251740735442203</v>
+        <v>0.07290191277999314</v>
       </c>
       <c r="T7">
-        <v>0.5493380157653899</v>
+        <v>0.5572438520141045</v>
       </c>
       <c r="U7">
-        <v>0.1468</v>
+        <v>0.2358</v>
       </c>
       <c r="V7">
-        <v>0.1948703349736332</v>
+        <v>0.1010989722014749</v>
       </c>
       <c r="W7">
-        <v>0.1181930348258707</v>
+        <v>0.2119608623548922</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y7">
-        <v>0.8119597290568049</v>
+        <v>0.4212457175061456</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08124544975448708</v>
+        <v>0.08314544975448709</v>
       </c>
       <c r="C8">
-        <v>547.0511005907896</v>
+        <v>514.735699429801</v>
       </c>
       <c r="D8">
-        <v>445.5391005907896</v>
+        <v>422.871699429801</v>
       </c>
       <c r="E8">
-        <v>-782.4119999999999</v>
+        <v>-772.764</v>
       </c>
       <c r="F8">
-        <v>57.888</v>
+        <v>67.53599999999999</v>
       </c>
       <c r="G8">
         <v>159.4</v>
@@ -1943,37 +1943,37 @@
         <v>5.75</v>
       </c>
       <c r="M8">
-        <v>13.6499904</v>
+        <v>15.9249888</v>
       </c>
       <c r="N8">
-        <v>-7.8999904</v>
+        <v>-10.1749888</v>
       </c>
       <c r="O8">
-        <v>-1.895997696</v>
+        <v>-2.441997311999999</v>
       </c>
       <c r="P8">
-        <v>-6.003992704</v>
+        <v>-7.732991487999998</v>
       </c>
       <c r="Q8">
-        <v>-3.033992704</v>
+        <v>-4.762991487999997</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07290191277999314</v>
+        <v>0.07319333119698232</v>
       </c>
       <c r="T8">
-        <v>0.5572438520141045</v>
+        <v>0.5632357213906003</v>
       </c>
       <c r="U8">
         <v>0.2358</v>
       </c>
       <c r="V8">
-        <v>0.101098972201475</v>
+        <v>0.08665626188697854</v>
       </c>
       <c r="W8">
-        <v>0.2119608623548922</v>
+        <v>0.2153664534470505</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>0.4212457175061456</v>
+        <v>0.3610677578624106</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08314544975448709</v>
+        <v>0.08504544975448709</v>
       </c>
       <c r="C9">
-        <v>514.7356994298009</v>
+        <v>484.6151036526368</v>
       </c>
       <c r="D9">
-        <v>422.871699429801</v>
+        <v>402.3991036526367</v>
       </c>
       <c r="E9">
-        <v>-772.7639999999999</v>
+        <v>-763.116</v>
       </c>
       <c r="F9">
-        <v>67.536</v>
+        <v>77.184</v>
       </c>
       <c r="G9">
         <v>159.4</v>
@@ -2025,37 +2025,37 @@
         <v>5.75</v>
       </c>
       <c r="M9">
-        <v>15.9249888</v>
+        <v>18.1999872</v>
       </c>
       <c r="N9">
-        <v>-10.1749888</v>
+        <v>-12.4499872</v>
       </c>
       <c r="O9">
-        <v>-2.441997312</v>
+        <v>-2.987996928</v>
       </c>
       <c r="P9">
-        <v>-7.732991488000001</v>
+        <v>-9.461990272</v>
       </c>
       <c r="Q9">
-        <v>-4.762991488000001</v>
+        <v>-6.491990271999999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07319333119698232</v>
+        <v>0.07349108479694952</v>
       </c>
       <c r="T9">
-        <v>0.5632357213906003</v>
+        <v>0.5693578487970198</v>
       </c>
       <c r="U9">
         <v>0.2358</v>
       </c>
       <c r="V9">
-        <v>0.08665626188697852</v>
+        <v>0.07582422915110622</v>
       </c>
       <c r="W9">
-        <v>0.2153664534470505</v>
+        <v>0.2179206467661692</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>0.3610677578624105</v>
+        <v>0.3159342881296092</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08504544975448709</v>
+        <v>0.08694544975448709</v>
       </c>
       <c r="C10">
-        <v>484.6151036526368</v>
+        <v>456.3852604232617</v>
       </c>
       <c r="D10">
-        <v>402.3991036526367</v>
+        <v>383.8172604232617</v>
       </c>
       <c r="E10">
-        <v>-763.116</v>
+        <v>-753.468</v>
       </c>
       <c r="F10">
-        <v>77.184</v>
+        <v>86.83199999999999</v>
       </c>
       <c r="G10">
         <v>159.4</v>
@@ -2107,37 +2107,37 @@
         <v>5.75</v>
       </c>
       <c r="M10">
-        <v>18.1999872</v>
+        <v>20.4749856</v>
       </c>
       <c r="N10">
-        <v>-12.4499872</v>
+        <v>-14.7249856</v>
       </c>
       <c r="O10">
-        <v>-2.987996928</v>
+        <v>-3.533996544</v>
       </c>
       <c r="P10">
-        <v>-9.461990272</v>
+        <v>-11.190989056</v>
       </c>
       <c r="Q10">
-        <v>-6.491990271999999</v>
+        <v>-8.220989055999999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07349108479694952</v>
+        <v>0.07379538243208084</v>
       </c>
       <c r="T10">
-        <v>0.5693578487970198</v>
+        <v>0.57561452845413</v>
       </c>
       <c r="U10">
         <v>0.2358</v>
       </c>
       <c r="V10">
-        <v>0.07582422915110622</v>
+        <v>0.0673993148009833</v>
       </c>
       <c r="W10">
-        <v>0.2179206467661692</v>
+        <v>0.2199072415699282</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>0.3159342881296092</v>
+        <v>0.2808304783374305</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08694544975448709</v>
+        <v>0.08884544975448709</v>
       </c>
       <c r="C11">
-        <v>456.3852604232617</v>
+        <v>429.7957997354644</v>
       </c>
       <c r="D11">
-        <v>383.8172604232617</v>
+        <v>366.8757997354644</v>
       </c>
       <c r="E11">
-        <v>-753.468</v>
+        <v>-743.8199999999999</v>
       </c>
       <c r="F11">
-        <v>86.83199999999999</v>
+        <v>96.47999999999999</v>
       </c>
       <c r="G11">
         <v>159.4</v>
@@ -2189,37 +2189,37 @@
         <v>5.75</v>
       </c>
       <c r="M11">
-        <v>20.4749856</v>
+        <v>22.749984</v>
       </c>
       <c r="N11">
-        <v>-14.7249856</v>
+        <v>-16.999984</v>
       </c>
       <c r="O11">
-        <v>-3.533996544</v>
+        <v>-4.079996159999999</v>
       </c>
       <c r="P11">
-        <v>-11.190989056</v>
+        <v>-12.91998784</v>
       </c>
       <c r="Q11">
-        <v>-8.220989055999999</v>
+        <v>-9.949987839999997</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07379538243208084</v>
+        <v>0.07410644223688173</v>
       </c>
       <c r="T11">
-        <v>0.57561452845413</v>
+        <v>0.5820102454369536</v>
       </c>
       <c r="U11">
         <v>0.2358</v>
       </c>
       <c r="V11">
-        <v>0.0673993148009833</v>
+        <v>0.06065938332088498</v>
       </c>
       <c r="W11">
-        <v>0.2199072415699282</v>
+        <v>0.2214965174129353</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>0.2808304783374305</v>
+        <v>0.2527474305036874</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08884544975448709</v>
+        <v>0.09074544975448709</v>
       </c>
       <c r="C12">
-        <v>429.7957997354644</v>
+        <v>404.6386876161048</v>
       </c>
       <c r="D12">
-        <v>366.8757997354644</v>
+        <v>351.3666876161048</v>
       </c>
       <c r="E12">
-        <v>-743.8199999999999</v>
+        <v>-734.1719999999999</v>
       </c>
       <c r="F12">
-        <v>96.48</v>
+        <v>106.128</v>
       </c>
       <c r="G12">
         <v>159.4</v>
@@ -2271,37 +2271,37 @@
         <v>5.75</v>
       </c>
       <c r="M12">
-        <v>22.749984</v>
+        <v>25.0249824</v>
       </c>
       <c r="N12">
-        <v>-16.999984</v>
+        <v>-19.2749824</v>
       </c>
       <c r="O12">
-        <v>-4.07999616</v>
+        <v>-4.625995776000001</v>
       </c>
       <c r="P12">
-        <v>-12.91998784</v>
+        <v>-14.648986624</v>
       </c>
       <c r="Q12">
-        <v>-9.94998784</v>
+        <v>-11.678986624</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07410644223688173</v>
+        <v>0.07442449214965569</v>
       </c>
       <c r="T12">
-        <v>0.5820102454369536</v>
+        <v>0.5885496863969194</v>
       </c>
       <c r="U12">
         <v>0.2358</v>
       </c>
       <c r="V12">
-        <v>0.06065938332088497</v>
+        <v>0.05514489392807724</v>
       </c>
       <c r="W12">
-        <v>0.2214965174129353</v>
+        <v>0.2227968340117594</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>0.2527474305036874</v>
+        <v>0.2297703913669885</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09074544975448709</v>
+        <v>0.09264544975448707</v>
       </c>
       <c r="C13">
-        <v>404.6386876161048</v>
+        <v>380.7396406100581</v>
       </c>
       <c r="D13">
-        <v>351.3666876161048</v>
+        <v>337.1156406100581</v>
       </c>
       <c r="E13">
-        <v>-734.1719999999999</v>
+        <v>-724.524</v>
       </c>
       <c r="F13">
-        <v>106.128</v>
+        <v>115.776</v>
       </c>
       <c r="G13">
         <v>159.4</v>
@@ -2353,37 +2353,37 @@
         <v>5.75</v>
       </c>
       <c r="M13">
-        <v>25.0249824</v>
+        <v>27.2999808</v>
       </c>
       <c r="N13">
-        <v>-19.2749824</v>
+        <v>-21.5499808</v>
       </c>
       <c r="O13">
-        <v>-4.625995776000001</v>
+        <v>-5.171995391999999</v>
       </c>
       <c r="P13">
-        <v>-14.648986624</v>
+        <v>-16.377985408</v>
       </c>
       <c r="Q13">
-        <v>-11.678986624</v>
+        <v>-13.407985408</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07442449214965569</v>
+        <v>0.07474977046953812</v>
       </c>
       <c r="T13">
-        <v>0.5885496863969194</v>
+        <v>0.5952377510150662</v>
       </c>
       <c r="U13">
         <v>0.2358</v>
       </c>
       <c r="V13">
-        <v>0.05514489392807724</v>
+        <v>0.05054948610073748</v>
       </c>
       <c r="W13">
-        <v>0.2227968340117594</v>
+        <v>0.2238804311774461</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>0.2297703913669885</v>
+        <v>0.2106228587530729</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09264544975448707</v>
+        <v>0.09454544975448709</v>
       </c>
       <c r="C14">
-        <v>380.7396406100581</v>
+        <v>357.9515481422447</v>
       </c>
       <c r="D14">
-        <v>337.1156406100581</v>
+        <v>323.9755481422447</v>
       </c>
       <c r="E14">
-        <v>-724.524</v>
+        <v>-714.876</v>
       </c>
       <c r="F14">
-        <v>115.776</v>
+        <v>125.424</v>
       </c>
       <c r="G14">
         <v>159.4</v>
@@ -2435,37 +2435,37 @@
         <v>5.75</v>
       </c>
       <c r="M14">
-        <v>27.2999808</v>
+        <v>29.5749792</v>
       </c>
       <c r="N14">
-        <v>-21.5499808</v>
+        <v>-23.8249792</v>
       </c>
       <c r="O14">
-        <v>-5.171995391999999</v>
+        <v>-5.717995007999999</v>
       </c>
       <c r="P14">
-        <v>-16.377985408</v>
+        <v>-18.106984192</v>
       </c>
       <c r="Q14">
-        <v>-13.407985408</v>
+        <v>-15.136984192</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07474977046953812</v>
+        <v>0.07508252645194662</v>
       </c>
       <c r="T14">
-        <v>0.5952377510150662</v>
+        <v>0.6020795642451244</v>
       </c>
       <c r="U14">
         <v>0.2358</v>
       </c>
       <c r="V14">
-        <v>0.05054948610073748</v>
+        <v>0.04666106409298845</v>
       </c>
       <c r="W14">
-        <v>0.2238804311774461</v>
+        <v>0.2247973210868733</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>0.2106228587530729</v>
+        <v>0.1944211003874519</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09454544975448709</v>
+        <v>0.0964454497544871</v>
       </c>
       <c r="C15">
-        <v>357.9515481422447</v>
+        <v>336.1493754682083</v>
       </c>
       <c r="D15">
-        <v>323.9755481422447</v>
+        <v>311.8213754682083</v>
       </c>
       <c r="E15">
-        <v>-714.876</v>
+        <v>-705.228</v>
       </c>
       <c r="F15">
-        <v>125.424</v>
+        <v>135.072</v>
       </c>
       <c r="G15">
         <v>159.4</v>
@@ -2517,37 +2517,37 @@
         <v>5.75</v>
       </c>
       <c r="M15">
-        <v>29.5749792</v>
+        <v>31.8499776</v>
       </c>
       <c r="N15">
-        <v>-23.8249792</v>
+        <v>-26.0999776</v>
       </c>
       <c r="O15">
-        <v>-5.717995007999999</v>
+        <v>-6.263994624</v>
       </c>
       <c r="P15">
-        <v>-18.106984192</v>
+        <v>-19.835982976</v>
       </c>
       <c r="Q15">
-        <v>-15.136984192</v>
+        <v>-16.86598297600001</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07508252645194662</v>
+        <v>0.0754230209455739</v>
       </c>
       <c r="T15">
-        <v>0.6020795642451244</v>
+        <v>0.6090804894107654</v>
       </c>
       <c r="U15">
         <v>0.2358</v>
       </c>
       <c r="V15">
-        <v>0.04666106409298845</v>
+        <v>0.04332813094348926</v>
       </c>
       <c r="W15">
-        <v>0.2247973210868733</v>
+        <v>0.2255832267235252</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>0.1944211003874519</v>
+        <v>0.1805338789312053</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.0964454497544871</v>
+        <v>0.09834544975448709</v>
       </c>
       <c r="C16">
-        <v>336.1493754682083</v>
+        <v>315.2261724552395</v>
       </c>
       <c r="D16">
-        <v>311.8213754682083</v>
+        <v>300.5461724552395</v>
       </c>
       <c r="E16">
-        <v>-705.228</v>
+        <v>-695.5799999999999</v>
       </c>
       <c r="F16">
-        <v>135.072</v>
+        <v>144.72</v>
       </c>
       <c r="G16">
         <v>159.4</v>
@@ -2599,37 +2599,37 @@
         <v>5.75</v>
       </c>
       <c r="M16">
-        <v>31.8499776</v>
+        <v>34.12497600000001</v>
       </c>
       <c r="N16">
-        <v>-26.0999776</v>
+        <v>-28.37497600000001</v>
       </c>
       <c r="O16">
-        <v>-6.263994624</v>
+        <v>-6.809994240000003</v>
       </c>
       <c r="P16">
-        <v>-19.835982976</v>
+        <v>-21.56498176000001</v>
       </c>
       <c r="Q16">
-        <v>-16.86598297600001</v>
+        <v>-18.59498176000001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.0754230209455739</v>
+        <v>0.07577152707434535</v>
       </c>
       <c r="T16">
-        <v>0.6090804894107654</v>
+        <v>0.6162461422273626</v>
       </c>
       <c r="U16">
         <v>0.2358</v>
       </c>
       <c r="V16">
-        <v>0.04332813094348926</v>
+        <v>0.04043958888058997</v>
       </c>
       <c r="W16">
-        <v>0.2255832267235252</v>
+        <v>0.2262643449419569</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>0.1805338789312053</v>
+        <v>0.1684982870024582</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09834544975448709</v>
+        <v>0.1002454497544871</v>
       </c>
       <c r="C17">
-        <v>315.2261724552395</v>
+        <v>295.0899180604287</v>
       </c>
       <c r="D17">
-        <v>300.5461724552395</v>
+        <v>290.0579180604287</v>
       </c>
       <c r="E17">
-        <v>-695.5799999999999</v>
+        <v>-685.932</v>
       </c>
       <c r="F17">
-        <v>144.72</v>
+        <v>154.368</v>
       </c>
       <c r="G17">
         <v>159.4</v>
@@ -2681,37 +2681,37 @@
         <v>5.75</v>
       </c>
       <c r="M17">
-        <v>34.124976</v>
+        <v>36.3999744</v>
       </c>
       <c r="N17">
-        <v>-28.374976</v>
+        <v>-30.6499744</v>
       </c>
       <c r="O17">
-        <v>-6.809994240000001</v>
+        <v>-7.355993856</v>
       </c>
       <c r="P17">
-        <v>-21.56498176</v>
+        <v>-23.293980544</v>
       </c>
       <c r="Q17">
-        <v>-18.59498176</v>
+        <v>-20.323980544</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07577152707434535</v>
+        <v>0.07612833096808756</v>
       </c>
       <c r="T17">
-        <v>0.6162461422273626</v>
+        <v>0.6235824058253074</v>
       </c>
       <c r="U17">
         <v>0.2358</v>
       </c>
       <c r="V17">
-        <v>0.04043958888058998</v>
+        <v>0.03791211457555311</v>
       </c>
       <c r="W17">
-        <v>0.2262643449419569</v>
+        <v>0.2268603233830846</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.1684982870024583</v>
+        <v>0.1579671440648046</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1002454497544871</v>
+        <v>0.1021454497544871</v>
       </c>
       <c r="C18">
-        <v>295.0899180604287</v>
+        <v>275.6610032444825</v>
       </c>
       <c r="D18">
-        <v>290.0579180604287</v>
+        <v>280.2770032444824</v>
       </c>
       <c r="E18">
-        <v>-685.932</v>
+        <v>-676.284</v>
       </c>
       <c r="F18">
-        <v>154.368</v>
+        <v>164.016</v>
       </c>
       <c r="G18">
         <v>159.4</v>
@@ -2763,37 +2763,37 @@
         <v>5.75</v>
       </c>
       <c r="M18">
-        <v>36.3999744</v>
+        <v>38.6749728</v>
       </c>
       <c r="N18">
-        <v>-30.6499744</v>
+        <v>-32.9249728</v>
       </c>
       <c r="O18">
-        <v>-7.355993856</v>
+        <v>-7.901993471999999</v>
       </c>
       <c r="P18">
-        <v>-23.293980544</v>
+        <v>-25.022979328</v>
       </c>
       <c r="Q18">
-        <v>-20.323980544</v>
+        <v>-22.052979328</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07612833096808756</v>
+        <v>0.07649373254601632</v>
       </c>
       <c r="T18">
-        <v>0.6235824058253074</v>
+        <v>0.6310954468593473</v>
       </c>
       <c r="U18">
         <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>0.03791211457555311</v>
+        <v>0.03568199018875587</v>
       </c>
       <c r="W18">
-        <v>0.2268603233830846</v>
+        <v>0.2273861867134914</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>0.1579671440648046</v>
+        <v>0.1486749591198161</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1021454497544871</v>
+        <v>0.1040454497544871</v>
       </c>
       <c r="C19">
-        <v>275.6610032444825</v>
+        <v>256.8702065383159</v>
       </c>
       <c r="D19">
-        <v>280.2770032444824</v>
+        <v>271.1342065383159</v>
       </c>
       <c r="E19">
-        <v>-676.284</v>
+        <v>-666.636</v>
       </c>
       <c r="F19">
-        <v>164.016</v>
+        <v>173.664</v>
       </c>
       <c r="G19">
         <v>159.4</v>
@@ -2845,37 +2845,37 @@
         <v>5.75</v>
       </c>
       <c r="M19">
-        <v>38.6749728</v>
+        <v>40.94997120000001</v>
       </c>
       <c r="N19">
-        <v>-32.9249728</v>
+        <v>-35.19997120000001</v>
       </c>
       <c r="O19">
-        <v>-7.901993471999999</v>
+        <v>-8.447993088000002</v>
       </c>
       <c r="P19">
-        <v>-25.022979328</v>
+        <v>-26.751978112</v>
       </c>
       <c r="Q19">
-        <v>-22.052979328</v>
+        <v>-23.781978112</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07649373254601632</v>
+        <v>0.07686804635755311</v>
       </c>
       <c r="T19">
-        <v>0.6310954468593473</v>
+        <v>0.6387917327966564</v>
       </c>
       <c r="U19">
         <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>0.03568199018875587</v>
+        <v>0.03369965740049164</v>
       </c>
       <c r="W19">
-        <v>0.2273861867134914</v>
+        <v>0.2278536207849641</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.1486749591198161</v>
+        <v>0.1404152391687152</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1040454497544871</v>
+        <v>0.1059454497544871</v>
       </c>
       <c r="C20">
-        <v>256.8702065383158</v>
+        <v>238.6570533218107</v>
       </c>
       <c r="D20">
-        <v>271.1342065383158</v>
+        <v>262.5690533218106</v>
       </c>
       <c r="E20">
-        <v>-666.636</v>
+        <v>-656.9879999999999</v>
       </c>
       <c r="F20">
-        <v>173.664</v>
+        <v>183.312</v>
       </c>
       <c r="G20">
         <v>159.4</v>
@@ -2927,37 +2927,37 @@
         <v>5.75</v>
       </c>
       <c r="M20">
-        <v>40.9499712</v>
+        <v>43.22496959999999</v>
       </c>
       <c r="N20">
-        <v>-35.1999712</v>
+        <v>-37.47496959999999</v>
       </c>
       <c r="O20">
-        <v>-8.447993088</v>
+        <v>-8.993992703999998</v>
       </c>
       <c r="P20">
-        <v>-26.751978112</v>
+        <v>-28.48097689599999</v>
       </c>
       <c r="Q20">
-        <v>-23.781978112</v>
+        <v>-25.510976896</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07686804635755311</v>
+        <v>0.07725160248542415</v>
       </c>
       <c r="T20">
-        <v>0.6387917327966564</v>
+        <v>0.6466780504855041</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>0.03369965740049165</v>
+        <v>0.03192599122151841</v>
       </c>
       <c r="W20">
-        <v>0.2278536207849641</v>
+        <v>0.228271851269966</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.1404152391687152</v>
+        <v>0.1330249634229934</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1059454497544871</v>
+        <v>0.1078454497544871</v>
       </c>
       <c r="C21">
-        <v>238.6570533218107</v>
+        <v>220.968476562588</v>
       </c>
       <c r="D21">
-        <v>262.5690533218106</v>
+        <v>254.528476562588</v>
       </c>
       <c r="E21">
-        <v>-656.9879999999999</v>
+        <v>-647.3399999999999</v>
       </c>
       <c r="F21">
-        <v>183.312</v>
+        <v>192.96</v>
       </c>
       <c r="G21">
         <v>159.4</v>
@@ -3009,37 +3009,37 @@
         <v>5.75</v>
       </c>
       <c r="M21">
-        <v>43.22496959999999</v>
+        <v>45.499968</v>
       </c>
       <c r="N21">
-        <v>-37.47496959999999</v>
+        <v>-39.749968</v>
       </c>
       <c r="O21">
-        <v>-8.993992703999998</v>
+        <v>-9.53999232</v>
       </c>
       <c r="P21">
-        <v>-28.48097689599999</v>
+        <v>-30.20997568</v>
       </c>
       <c r="Q21">
-        <v>-25.510976896</v>
+        <v>-27.23997568</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07725160248542415</v>
+        <v>0.07764474751649195</v>
       </c>
       <c r="T21">
-        <v>0.6466780504855041</v>
+        <v>0.6547615261165728</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>0.03192599122151841</v>
+        <v>0.03032969166044248</v>
       </c>
       <c r="W21">
-        <v>0.228271851269966</v>
+        <v>0.2286482587064677</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.1330249634229934</v>
+        <v>0.1263737152518437</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1078454497544871</v>
+        <v>0.1097454497544871</v>
       </c>
       <c r="C22">
-        <v>220.968476562588</v>
+        <v>203.7577163141938</v>
       </c>
       <c r="D22">
-        <v>254.528476562588</v>
+        <v>246.9657163141938</v>
       </c>
       <c r="E22">
-        <v>-647.3399999999999</v>
+        <v>-637.692</v>
       </c>
       <c r="F22">
-        <v>192.96</v>
+        <v>202.608</v>
       </c>
       <c r="G22">
         <v>159.4</v>
@@ -3091,37 +3091,37 @@
         <v>5.75</v>
       </c>
       <c r="M22">
-        <v>45.499968</v>
+        <v>47.7749664</v>
       </c>
       <c r="N22">
-        <v>-39.749968</v>
+        <v>-42.0249664</v>
       </c>
       <c r="O22">
-        <v>-9.53999232</v>
+        <v>-10.085991936</v>
       </c>
       <c r="P22">
-        <v>-30.20997568</v>
+        <v>-31.938974464</v>
       </c>
       <c r="Q22">
-        <v>-27.23997568</v>
+        <v>-28.96897446400001</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07764474751649195</v>
+        <v>0.07804784558632095</v>
       </c>
       <c r="T22">
-        <v>0.6547615261165728</v>
+        <v>0.663049646700327</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>0.03032969166044248</v>
+        <v>0.02888542062899284</v>
       </c>
       <c r="W22">
-        <v>0.2286482587064677</v>
+        <v>0.2289888178156835</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.1263737152518437</v>
+        <v>0.1203559192874701</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1097454497544871</v>
+        <v>0.1116454497544871</v>
       </c>
       <c r="C23">
-        <v>203.757716314194</v>
+        <v>186.9834097471255</v>
       </c>
       <c r="D23">
-        <v>246.9657163141939</v>
+        <v>239.8394097471255</v>
       </c>
       <c r="E23">
-        <v>-637.692</v>
+        <v>-628.044</v>
       </c>
       <c r="F23">
-        <v>202.608</v>
+        <v>212.256</v>
       </c>
       <c r="G23">
         <v>159.4</v>
@@ -3173,37 +3173,37 @@
         <v>5.75</v>
       </c>
       <c r="M23">
-        <v>47.7749664</v>
+        <v>50.04996480000001</v>
       </c>
       <c r="N23">
-        <v>-42.0249664</v>
+        <v>-44.29996480000001</v>
       </c>
       <c r="O23">
-        <v>-10.085991936</v>
+        <v>-10.631991552</v>
       </c>
       <c r="P23">
-        <v>-31.938974464</v>
+        <v>-33.667973248</v>
       </c>
       <c r="Q23">
-        <v>-28.968974464</v>
+        <v>-30.697973248</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07804784558632095</v>
+        <v>0.07846127950409429</v>
       </c>
       <c r="T23">
-        <v>0.663049646700327</v>
+        <v>0.6715502831964849</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>0.02888542062899285</v>
+        <v>0.02757244696403862</v>
       </c>
       <c r="W23">
-        <v>0.2289888178156835</v>
+        <v>0.2292984170058797</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.1203559192874702</v>
+        <v>0.1148851956834942</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1116454497544871</v>
+        <v>0.1135454497544871</v>
       </c>
       <c r="C24">
-        <v>186.9834097471255</v>
+        <v>170.6088343066938</v>
       </c>
       <c r="D24">
-        <v>239.8394097471255</v>
+        <v>233.1128343066938</v>
       </c>
       <c r="E24">
-        <v>-628.044</v>
+        <v>-618.396</v>
       </c>
       <c r="F24">
-        <v>212.256</v>
+        <v>221.904</v>
       </c>
       <c r="G24">
         <v>159.4</v>
@@ -3255,37 +3255,37 @@
         <v>5.75</v>
       </c>
       <c r="M24">
-        <v>50.04996480000001</v>
+        <v>52.3249632</v>
       </c>
       <c r="N24">
-        <v>-44.29996480000001</v>
+        <v>-46.5749632</v>
       </c>
       <c r="O24">
-        <v>-10.631991552</v>
+        <v>-11.177991168</v>
       </c>
       <c r="P24">
-        <v>-33.667973248</v>
+        <v>-35.396972032</v>
       </c>
       <c r="Q24">
-        <v>-30.697973248</v>
+        <v>-32.426972032</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07846127950409429</v>
+        <v>0.07888545196518643</v>
       </c>
       <c r="T24">
-        <v>0.6715502831964849</v>
+        <v>0.68027171544579</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.02757244696403862</v>
+        <v>0.0263736449221239</v>
       </c>
       <c r="W24">
-        <v>0.2292984170058797</v>
+        <v>0.2295810945273632</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.1148851956834942</v>
+        <v>0.1098901871755162</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1135454497544871</v>
+        <v>0.1154454497544871</v>
       </c>
       <c r="C25">
-        <v>170.6088343066938</v>
+        <v>154.6012747555088</v>
       </c>
       <c r="D25">
-        <v>233.1128343066938</v>
+        <v>226.7532747555088</v>
       </c>
       <c r="E25">
-        <v>-618.396</v>
+        <v>-608.7479999999999</v>
       </c>
       <c r="F25">
-        <v>221.904</v>
+        <v>231.552</v>
       </c>
       <c r="G25">
         <v>159.4</v>
@@ -3337,37 +3337,37 @@
         <v>5.75</v>
       </c>
       <c r="M25">
-        <v>52.3249632</v>
+        <v>54.59996160000001</v>
       </c>
       <c r="N25">
-        <v>-46.5749632</v>
+        <v>-48.84996160000001</v>
       </c>
       <c r="O25">
-        <v>-11.177991168</v>
+        <v>-11.723990784</v>
       </c>
       <c r="P25">
-        <v>-35.396972032</v>
+        <v>-37.12597081600001</v>
       </c>
       <c r="Q25">
-        <v>-32.426972032</v>
+        <v>-34.15597081600001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07888545196518643</v>
+        <v>0.0793207868594652</v>
       </c>
       <c r="T25">
-        <v>0.68027171544579</v>
+        <v>0.6892226590700767</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.0263736449221239</v>
+        <v>0.02527474305036874</v>
       </c>
       <c r="W25">
-        <v>0.2295810945273632</v>
+        <v>0.2298402155887231</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.1098901871755162</v>
+        <v>0.1053114293765364</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1154454497544871</v>
+        <v>0.1173454497544871</v>
       </c>
       <c r="C26">
-        <v>154.6012747555088</v>
+        <v>138.9314910709573</v>
       </c>
       <c r="D26">
-        <v>226.7532747555088</v>
+        <v>220.7314910709573</v>
       </c>
       <c r="E26">
-        <v>-608.7479999999999</v>
+        <v>-599.0999999999999</v>
       </c>
       <c r="F26">
-        <v>231.552</v>
+        <v>241.2</v>
       </c>
       <c r="G26">
         <v>159.4</v>
@@ -3419,37 +3419,37 @@
         <v>5.75</v>
       </c>
       <c r="M26">
-        <v>54.5999616</v>
+        <v>56.87496</v>
       </c>
       <c r="N26">
-        <v>-48.8499616</v>
+        <v>-51.12496</v>
       </c>
       <c r="O26">
-        <v>-11.723990784</v>
+        <v>-12.2699904</v>
       </c>
       <c r="P26">
-        <v>-37.125970816</v>
+        <v>-38.8549696</v>
       </c>
       <c r="Q26">
-        <v>-34.155970816</v>
+        <v>-35.88496960000001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.0793207868594652</v>
+        <v>0.07976773068425808</v>
       </c>
       <c r="T26">
-        <v>0.6892226590700767</v>
+        <v>0.6984122945243443</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.02527474305036874</v>
+        <v>0.02426375332835399</v>
       </c>
       <c r="W26">
-        <v>0.2298402155887231</v>
+        <v>0.2300786069651742</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.1053114293765364</v>
+        <v>0.1010989722014749</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1173454497544871</v>
+        <v>0.1192454497544871</v>
       </c>
       <c r="C27">
-        <v>138.9314910709573</v>
+        <v>123.573268934164</v>
       </c>
       <c r="D27">
-        <v>220.7314910709573</v>
+        <v>215.021268934164</v>
       </c>
       <c r="E27">
-        <v>-599.0999999999999</v>
+        <v>-589.452</v>
       </c>
       <c r="F27">
-        <v>241.2</v>
+        <v>250.848</v>
       </c>
       <c r="G27">
         <v>159.4</v>
@@ -3501,37 +3501,37 @@
         <v>5.75</v>
       </c>
       <c r="M27">
-        <v>56.87496</v>
+        <v>59.1499584</v>
       </c>
       <c r="N27">
-        <v>-51.12496</v>
+        <v>-53.3999584</v>
       </c>
       <c r="O27">
-        <v>-12.2699904</v>
+        <v>-12.815990016</v>
       </c>
       <c r="P27">
-        <v>-38.8549696</v>
+        <v>-40.58396838399999</v>
       </c>
       <c r="Q27">
-        <v>-35.88496960000001</v>
+        <v>-37.613968384</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07976773068425808</v>
+        <v>0.08022675407188318</v>
       </c>
       <c r="T27">
-        <v>0.6984122945243443</v>
+        <v>0.7078502985044031</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.02426375332835399</v>
+        <v>0.02333053204649422</v>
       </c>
       <c r="W27">
-        <v>0.2300786069651742</v>
+        <v>0.2302986605434367</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.1010989722014749</v>
+        <v>0.09721055019372593</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1192454497544871</v>
+        <v>0.1211454497544871</v>
       </c>
       <c r="C28">
-        <v>123.573268934164</v>
+        <v>108.503038231366</v>
       </c>
       <c r="D28">
-        <v>215.021268934164</v>
+        <v>209.599038231366</v>
       </c>
       <c r="E28">
-        <v>-589.452</v>
+        <v>-579.804</v>
       </c>
       <c r="F28">
-        <v>250.848</v>
+        <v>260.496</v>
       </c>
       <c r="G28">
         <v>159.4</v>
@@ -3583,37 +3583,37 @@
         <v>5.75</v>
       </c>
       <c r="M28">
-        <v>59.1499584</v>
+        <v>61.4249568</v>
       </c>
       <c r="N28">
-        <v>-53.3999584</v>
+        <v>-55.6749568</v>
       </c>
       <c r="O28">
-        <v>-12.815990016</v>
+        <v>-13.361989632</v>
       </c>
       <c r="P28">
-        <v>-40.58396838399999</v>
+        <v>-42.312967168</v>
       </c>
       <c r="Q28">
-        <v>-37.613968384</v>
+        <v>-39.342967168</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08022675407188318</v>
+        <v>0.08069835344273089</v>
       </c>
       <c r="T28">
-        <v>0.7078502985044031</v>
+        <v>0.7175468779359702</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.02333053204649422</v>
+        <v>0.02246643826699444</v>
       </c>
       <c r="W28">
-        <v>0.2302986605434367</v>
+        <v>0.2305024138566427</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.09721055019372593</v>
+        <v>0.09361015944581019</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1211454497544871</v>
+        <v>0.1230454497544871</v>
       </c>
       <c r="C29">
-        <v>108.503038231366</v>
+        <v>93.69954785743022</v>
       </c>
       <c r="D29">
-        <v>209.599038231366</v>
+        <v>204.4435478574302</v>
       </c>
       <c r="E29">
-        <v>-579.804</v>
+        <v>-570.1559999999999</v>
       </c>
       <c r="F29">
-        <v>260.496</v>
+        <v>270.144</v>
       </c>
       <c r="G29">
         <v>159.4</v>
@@ -3665,37 +3665,37 @@
         <v>5.75</v>
       </c>
       <c r="M29">
-        <v>61.4249568</v>
+        <v>63.69995520000001</v>
       </c>
       <c r="N29">
-        <v>-55.6749568</v>
+        <v>-57.94995520000001</v>
       </c>
       <c r="O29">
-        <v>-13.361989632</v>
+        <v>-13.907989248</v>
       </c>
       <c r="P29">
-        <v>-42.312967168</v>
+        <v>-44.04196595200001</v>
       </c>
       <c r="Q29">
-        <v>-39.342967168</v>
+        <v>-41.07196595200001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08069835344273089</v>
+        <v>0.08118305279610216</v>
       </c>
       <c r="T29">
-        <v>0.7175468779359702</v>
+        <v>0.7275128067961921</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.02246643826699444</v>
+        <v>0.02166406547174463</v>
       </c>
       <c r="W29">
-        <v>0.2305024138566427</v>
+        <v>0.2306916133617626</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.09361015944581019</v>
+        <v>0.0902669394656026</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1230454497544871</v>
+        <v>0.1249454497544871</v>
       </c>
       <c r="C30">
-        <v>93.69954785743022</v>
+        <v>79.14358736021785</v>
       </c>
       <c r="D30">
-        <v>204.4435478574302</v>
+        <v>199.5355873602179</v>
       </c>
       <c r="E30">
-        <v>-570.1559999999999</v>
+        <v>-560.5079999999999</v>
       </c>
       <c r="F30">
-        <v>270.144</v>
+        <v>279.792</v>
       </c>
       <c r="G30">
         <v>159.4</v>
@@ -3747,37 +3747,37 @@
         <v>5.75</v>
       </c>
       <c r="M30">
-        <v>63.69995520000001</v>
+        <v>65.97495360000001</v>
       </c>
       <c r="N30">
-        <v>-57.94995520000001</v>
+        <v>-60.22495360000001</v>
       </c>
       <c r="O30">
-        <v>-13.907989248</v>
+        <v>-14.453988864</v>
       </c>
       <c r="P30">
-        <v>-44.04196595200001</v>
+        <v>-45.770964736</v>
       </c>
       <c r="Q30">
-        <v>-41.07196595200001</v>
+        <v>-42.800964736</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08118305279610216</v>
+        <v>0.0816814056523853</v>
       </c>
       <c r="T30">
-        <v>0.7275128067961921</v>
+        <v>0.7377594660468427</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.02166406547174463</v>
+        <v>0.02091702873133965</v>
       </c>
       <c r="W30">
-        <v>0.2306916133617626</v>
+        <v>0.2308677646251501</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.0902669394656026</v>
+        <v>0.08715428638058187</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1249454497544871</v>
+        <v>0.1268454497544871</v>
       </c>
       <c r="C31">
-        <v>79.14358736021796</v>
+        <v>64.81774773895751</v>
       </c>
       <c r="D31">
-        <v>199.535587360218</v>
+        <v>194.8577477389575</v>
       </c>
       <c r="E31">
-        <v>-560.508</v>
+        <v>-550.8599999999999</v>
       </c>
       <c r="F31">
-        <v>279.792</v>
+        <v>289.44</v>
       </c>
       <c r="G31">
         <v>159.4</v>
@@ -3829,37 +3829,37 @@
         <v>5.75</v>
       </c>
       <c r="M31">
-        <v>65.97495359999999</v>
+        <v>68.24995200000001</v>
       </c>
       <c r="N31">
-        <v>-60.22495359999999</v>
+        <v>-62.49995200000001</v>
       </c>
       <c r="O31">
-        <v>-14.453988864</v>
+        <v>-14.99998848</v>
       </c>
       <c r="P31">
-        <v>-45.770964736</v>
+        <v>-47.49996352000001</v>
       </c>
       <c r="Q31">
-        <v>-42.800964736</v>
+        <v>-44.52996352000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08168140565238528</v>
+        <v>0.08219399716170508</v>
       </c>
       <c r="T31">
-        <v>0.7377594660468426</v>
+        <v>0.7482988869903689</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.02091702873133965</v>
+        <v>0.02021979444029499</v>
       </c>
       <c r="W31">
-        <v>0.2308677646251501</v>
+        <v>0.2310321724709785</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.08715428638058187</v>
+        <v>0.08424914350122914</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1268454497544871</v>
+        <v>0.1287454497544871</v>
       </c>
       <c r="C32">
-        <v>64.81774773895751</v>
+        <v>50.70621511842353</v>
       </c>
       <c r="D32">
-        <v>194.8577477389575</v>
+        <v>190.3942151184235</v>
       </c>
       <c r="E32">
-        <v>-550.8599999999999</v>
+        <v>-541.212</v>
       </c>
       <c r="F32">
-        <v>289.44</v>
+        <v>299.088</v>
       </c>
       <c r="G32">
         <v>159.4</v>
@@ -3911,37 +3911,37 @@
         <v>5.75</v>
       </c>
       <c r="M32">
-        <v>68.24995200000001</v>
+        <v>70.52495039999999</v>
       </c>
       <c r="N32">
-        <v>-62.49995200000001</v>
+        <v>-64.77495039999999</v>
       </c>
       <c r="O32">
-        <v>-14.99998848</v>
+        <v>-15.545988096</v>
       </c>
       <c r="P32">
-        <v>-47.49996352000001</v>
+        <v>-49.22896230399999</v>
       </c>
       <c r="Q32">
-        <v>-44.52996352000001</v>
+        <v>-46.25896230399999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08219399716170508</v>
+        <v>0.08272144639593268</v>
       </c>
       <c r="T32">
-        <v>0.7482988869903689</v>
+        <v>0.7591437983960265</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.02021979444029499</v>
+        <v>0.01956754300673709</v>
       </c>
       <c r="W32">
-        <v>0.2310321724709785</v>
+        <v>0.2311859733590114</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.08424914350122914</v>
+        <v>0.08153142919473788</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1287454497544871</v>
+        <v>0.1306454497544871</v>
       </c>
       <c r="C33">
-        <v>50.70621511842353</v>
+        <v>36.79459214545579</v>
       </c>
       <c r="D33">
-        <v>190.3942151184235</v>
+        <v>186.1305921454558</v>
       </c>
       <c r="E33">
-        <v>-541.212</v>
+        <v>-531.564</v>
       </c>
       <c r="F33">
-        <v>299.088</v>
+        <v>308.736</v>
       </c>
       <c r="G33">
         <v>159.4</v>
@@ -3993,37 +3993,37 @@
         <v>5.75</v>
       </c>
       <c r="M33">
-        <v>70.52495039999999</v>
+        <v>72.7999488</v>
       </c>
       <c r="N33">
-        <v>-64.77495039999999</v>
+        <v>-67.0499488</v>
       </c>
       <c r="O33">
-        <v>-15.545988096</v>
+        <v>-16.091987712</v>
       </c>
       <c r="P33">
-        <v>-49.22896230399999</v>
+        <v>-50.957961088</v>
       </c>
       <c r="Q33">
-        <v>-46.25896230399999</v>
+        <v>-47.987961088</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08272144639593268</v>
+        <v>0.08326440884293169</v>
       </c>
       <c r="T33">
-        <v>0.7591437983960265</v>
+        <v>0.7703076777842033</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.01956754300673709</v>
+        <v>0.01895605728777655</v>
       </c>
       <c r="W33">
-        <v>0.2311859733590114</v>
+        <v>0.2313301616915423</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.08153142919473788</v>
+        <v>0.07898357203240236</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1306454497544871</v>
+        <v>0.1325454497544871</v>
       </c>
       <c r="C34">
-        <v>36.79459214545579</v>
+        <v>23.06974285736874</v>
       </c>
       <c r="D34">
-        <v>186.1305921454558</v>
+        <v>182.0537428573688</v>
       </c>
       <c r="E34">
-        <v>-531.564</v>
+        <v>-521.9159999999999</v>
       </c>
       <c r="F34">
-        <v>308.736</v>
+        <v>318.384</v>
       </c>
       <c r="G34">
         <v>159.4</v>
@@ -4075,37 +4075,37 @@
         <v>5.75</v>
       </c>
       <c r="M34">
-        <v>72.7999488</v>
+        <v>75.07494720000001</v>
       </c>
       <c r="N34">
-        <v>-67.0499488</v>
+        <v>-69.32494720000001</v>
       </c>
       <c r="O34">
-        <v>-16.091987712</v>
+        <v>-16.637987328</v>
       </c>
       <c r="P34">
-        <v>-50.957961088</v>
+        <v>-52.68695987200001</v>
       </c>
       <c r="Q34">
-        <v>-47.987961088</v>
+        <v>-49.71695987200001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08326440884293169</v>
+        <v>0.08382357912416949</v>
       </c>
       <c r="T34">
-        <v>0.7703076777842033</v>
+        <v>0.7818048073033707</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.01895605728777655</v>
+        <v>0.01838163130935908</v>
       </c>
       <c r="W34">
-        <v>0.2313301616915423</v>
+        <v>0.2314656113372531</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.07898357203240236</v>
+        <v>0.07659013045566287</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1325454497544871</v>
+        <v>0.1344454497544871</v>
       </c>
       <c r="C35">
-        <v>23.06974285736874</v>
+        <v>9.519657500624476</v>
       </c>
       <c r="D35">
-        <v>182.0537428573688</v>
+        <v>178.1516575006245</v>
       </c>
       <c r="E35">
-        <v>-521.9159999999999</v>
+        <v>-512.268</v>
       </c>
       <c r="F35">
-        <v>318.384</v>
+        <v>328.032</v>
       </c>
       <c r="G35">
         <v>159.4</v>
@@ -4157,37 +4157,37 @@
         <v>5.75</v>
       </c>
       <c r="M35">
-        <v>75.07494720000001</v>
+        <v>77.3499456</v>
       </c>
       <c r="N35">
-        <v>-69.32494720000001</v>
+        <v>-71.5999456</v>
       </c>
       <c r="O35">
-        <v>-16.637987328</v>
+        <v>-17.183986944</v>
       </c>
       <c r="P35">
-        <v>-52.68695987200001</v>
+        <v>-54.415958656</v>
       </c>
       <c r="Q35">
-        <v>-49.71695987200001</v>
+        <v>-51.445958656</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08382357912416949</v>
+        <v>0.08439969395938418</v>
       </c>
       <c r="T35">
-        <v>0.7818048073033707</v>
+        <v>0.7936503346867549</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.01838163130935908</v>
+        <v>0.01784099509437793</v>
       </c>
       <c r="W35">
-        <v>0.2314656113372531</v>
+        <v>0.2315930933567457</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.07659013045566287</v>
+        <v>0.0743374795599081</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1344454497544871</v>
+        <v>0.1363454497544871</v>
       </c>
       <c r="C36">
-        <v>9.519657500624476</v>
+        <v>-3.866665630675868</v>
       </c>
       <c r="D36">
-        <v>178.1516575006245</v>
+        <v>174.4133343693241</v>
       </c>
       <c r="E36">
-        <v>-512.268</v>
+        <v>-502.6199999999999</v>
       </c>
       <c r="F36">
-        <v>328.032</v>
+        <v>337.68</v>
       </c>
       <c r="G36">
         <v>159.4</v>
@@ -4239,37 +4239,37 @@
         <v>5.75</v>
       </c>
       <c r="M36">
-        <v>77.3499456</v>
+        <v>79.624944</v>
       </c>
       <c r="N36">
-        <v>-71.5999456</v>
+        <v>-73.874944</v>
       </c>
       <c r="O36">
-        <v>-17.183986944</v>
+        <v>-17.72998656</v>
       </c>
       <c r="P36">
-        <v>-54.415958656</v>
+        <v>-56.14495744</v>
       </c>
       <c r="Q36">
-        <v>-51.445958656</v>
+        <v>-53.17495744</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08439969395938418</v>
+        <v>0.08499353540491317</v>
       </c>
       <c r="T36">
-        <v>0.7936503346867549</v>
+        <v>0.805860339835782</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.01784099509437793</v>
+        <v>0.01733125237739571</v>
       </c>
       <c r="W36">
-        <v>0.2315930933567457</v>
+        <v>0.2317132906894101</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.0743374795599081</v>
+        <v>0.0722135515724821</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1363454497544871</v>
+        <v>0.1382454497544871</v>
       </c>
       <c r="C37">
-        <v>-3.866665630675868</v>
+        <v>-17.09932378509882</v>
       </c>
       <c r="D37">
-        <v>174.4133343693241</v>
+        <v>170.8286762149012</v>
       </c>
       <c r="E37">
-        <v>-502.6199999999999</v>
+        <v>-492.9719999999999</v>
       </c>
       <c r="F37">
-        <v>337.68</v>
+        <v>347.328</v>
       </c>
       <c r="G37">
         <v>159.4</v>
@@ -4321,37 +4321,37 @@
         <v>5.75</v>
       </c>
       <c r="M37">
-        <v>79.624944</v>
+        <v>81.89994240000001</v>
       </c>
       <c r="N37">
-        <v>-73.874944</v>
+        <v>-76.14994240000001</v>
       </c>
       <c r="O37">
-        <v>-17.72998656</v>
+        <v>-18.275986176</v>
       </c>
       <c r="P37">
-        <v>-56.14495744</v>
+        <v>-57.87395622400001</v>
       </c>
       <c r="Q37">
-        <v>-53.17495744</v>
+        <v>-54.90395622400001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08499353540491317</v>
+        <v>0.08560593439561492</v>
       </c>
       <c r="T37">
-        <v>0.805860339835782</v>
+        <v>0.8184519076457161</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.01733125237739571</v>
+        <v>0.01684982870024582</v>
       </c>
       <c r="W37">
-        <v>0.2317132906894101</v>
+        <v>0.231826810392482</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.0722135515724821</v>
+        <v>0.07020761958435762</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1382454497544871</v>
+        <v>0.1401454497544871</v>
       </c>
       <c r="C38">
-        <v>-17.09932378509876</v>
+        <v>-30.18760082710713</v>
       </c>
       <c r="D38">
-        <v>170.8286762149012</v>
+        <v>167.3883991728929</v>
       </c>
       <c r="E38">
-        <v>-492.972</v>
+        <v>-483.324</v>
       </c>
       <c r="F38">
-        <v>347.328</v>
+        <v>356.976</v>
       </c>
       <c r="G38">
         <v>159.4</v>
@@ -4403,37 +4403,37 @@
         <v>5.75</v>
       </c>
       <c r="M38">
-        <v>81.8999424</v>
+        <v>84.1749408</v>
       </c>
       <c r="N38">
-        <v>-76.1499424</v>
+        <v>-78.4249408</v>
       </c>
       <c r="O38">
-        <v>-18.275986176</v>
+        <v>-18.821985792</v>
       </c>
       <c r="P38">
-        <v>-57.873956224</v>
+        <v>-59.602955008</v>
       </c>
       <c r="Q38">
-        <v>-54.903956224</v>
+        <v>-56.632955008</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08560593439561492</v>
+        <v>0.08623777462411675</v>
       </c>
       <c r="T38">
-        <v>0.8184519076457161</v>
+        <v>0.8314432077670766</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.01684982870024582</v>
+        <v>0.01639442792456351</v>
       </c>
       <c r="W38">
-        <v>0.231826810392482</v>
+        <v>0.2319341938953879</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.07020761958435762</v>
+        <v>0.06831011635234796</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1401454497544871</v>
+        <v>0.1420454497544871</v>
       </c>
       <c r="C39">
-        <v>-30.18760082710713</v>
+        <v>-43.1400475229226</v>
       </c>
       <c r="D39">
-        <v>167.3883991728929</v>
+        <v>164.0839524770774</v>
       </c>
       <c r="E39">
-        <v>-483.324</v>
+        <v>-473.676</v>
       </c>
       <c r="F39">
-        <v>356.976</v>
+        <v>366.624</v>
       </c>
       <c r="G39">
         <v>159.4</v>
@@ -4485,37 +4485,37 @@
         <v>5.75</v>
       </c>
       <c r="M39">
-        <v>84.1749408</v>
+        <v>86.44993919999999</v>
       </c>
       <c r="N39">
-        <v>-78.4249408</v>
+        <v>-80.69993919999999</v>
       </c>
       <c r="O39">
-        <v>-18.821985792</v>
+        <v>-19.367985408</v>
       </c>
       <c r="P39">
-        <v>-59.602955008</v>
+        <v>-61.33195379199999</v>
       </c>
       <c r="Q39">
-        <v>-56.632955008</v>
+        <v>-58.36195379199999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08623777462411675</v>
+        <v>0.08688999679547348</v>
       </c>
       <c r="T39">
-        <v>0.8314432077670766</v>
+        <v>0.8448535820859004</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.01639442792456351</v>
+        <v>0.0159629956107592</v>
       </c>
       <c r="W39">
-        <v>0.2319341938953879</v>
+        <v>0.232035925634983</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.06831011635234796</v>
+        <v>0.06651248171149671</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1420454497544871</v>
+        <v>0.1439454497544871</v>
       </c>
       <c r="C40">
-        <v>-43.1400475229226</v>
+        <v>-55.96455250085404</v>
       </c>
       <c r="D40">
-        <v>164.0839524770774</v>
+        <v>160.9074474991459</v>
       </c>
       <c r="E40">
-        <v>-473.676</v>
+        <v>-464.028</v>
       </c>
       <c r="F40">
-        <v>366.624</v>
+        <v>376.272</v>
       </c>
       <c r="G40">
         <v>159.4</v>
@@ -4567,37 +4567,37 @@
         <v>5.75</v>
       </c>
       <c r="M40">
-        <v>86.44993919999999</v>
+        <v>88.7249376</v>
       </c>
       <c r="N40">
-        <v>-80.69993919999999</v>
+        <v>-82.9749376</v>
       </c>
       <c r="O40">
-        <v>-19.367985408</v>
+        <v>-19.913985024</v>
       </c>
       <c r="P40">
-        <v>-61.33195379199999</v>
+        <v>-63.06095257600001</v>
       </c>
       <c r="Q40">
-        <v>-58.36195379199999</v>
+        <v>-60.09095257600001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08688999679547348</v>
+        <v>0.08756360330031729</v>
       </c>
       <c r="T40">
-        <v>0.8448535820859004</v>
+        <v>0.8587036408086201</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.0159629956107592</v>
+        <v>0.01555368803099614</v>
       </c>
       <c r="W40">
-        <v>0.232035925634983</v>
+        <v>0.2321324403622911</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.06651248171149671</v>
+        <v>0.06480703346248395</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1439454497544871</v>
+        <v>0.1458454497544871</v>
       </c>
       <c r="C41">
-        <v>-55.96455250085404</v>
+        <v>-68.66840512582235</v>
       </c>
       <c r="D41">
-        <v>160.9074474991459</v>
+        <v>157.8515948741777</v>
       </c>
       <c r="E41">
-        <v>-464.028</v>
+        <v>-454.3799999999999</v>
       </c>
       <c r="F41">
-        <v>376.272</v>
+        <v>385.92</v>
       </c>
       <c r="G41">
         <v>159.4</v>
@@ -4649,37 +4649,37 @@
         <v>5.75</v>
       </c>
       <c r="M41">
-        <v>88.7249376</v>
+        <v>90.99993600000001</v>
       </c>
       <c r="N41">
-        <v>-82.9749376</v>
+        <v>-85.24993600000001</v>
       </c>
       <c r="O41">
-        <v>-19.913985024</v>
+        <v>-20.45998464</v>
       </c>
       <c r="P41">
-        <v>-63.06095257600001</v>
+        <v>-64.78995136</v>
       </c>
       <c r="Q41">
-        <v>-60.09095257600001</v>
+        <v>-61.81995136</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08756360330031729</v>
+        <v>0.08825966335532259</v>
       </c>
       <c r="T41">
-        <v>0.8587036408086201</v>
+        <v>0.8730153681554303</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.01555368803099614</v>
+        <v>0.01516484583022124</v>
       </c>
       <c r="W41">
-        <v>0.2321324403622911</v>
+        <v>0.2322241293532338</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.06480703346248395</v>
+        <v>0.0631868576259218</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1458454497544871</v>
+        <v>0.1477454497544871</v>
       </c>
       <c r="C42">
-        <v>-68.66840512582235</v>
+        <v>-81.25835134297296</v>
       </c>
       <c r="D42">
-        <v>157.8515948741777</v>
+        <v>154.909648657027</v>
       </c>
       <c r="E42">
-        <v>-454.3799999999999</v>
+        <v>-444.732</v>
       </c>
       <c r="F42">
-        <v>385.92</v>
+        <v>395.568</v>
       </c>
       <c r="G42">
         <v>159.4</v>
@@ -4731,37 +4731,37 @@
         <v>5.75</v>
       </c>
       <c r="M42">
-        <v>90.99993600000001</v>
+        <v>93.27493440000001</v>
       </c>
       <c r="N42">
-        <v>-85.24993600000001</v>
+        <v>-87.52493440000001</v>
       </c>
       <c r="O42">
-        <v>-20.45998464</v>
+        <v>-21.005984256</v>
       </c>
       <c r="P42">
-        <v>-64.78995136</v>
+        <v>-66.518950144</v>
       </c>
       <c r="Q42">
-        <v>-61.81995136</v>
+        <v>-63.548950144</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08825966335532259</v>
+        <v>0.08897931866642975</v>
       </c>
       <c r="T42">
-        <v>0.8730153681554303</v>
+        <v>0.8878122388021327</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.01516484583022124</v>
+        <v>0.01479497154167926</v>
       </c>
       <c r="W42">
-        <v>0.2322241293532338</v>
+        <v>0.232311345710472</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.0631868576259218</v>
+        <v>0.06164571475699687</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1477454497544871</v>
+        <v>0.1496454497544871</v>
       </c>
       <c r="C43">
-        <v>-81.25835134297296</v>
+        <v>-93.74064339085965</v>
       </c>
       <c r="D43">
-        <v>154.909648657027</v>
+        <v>152.0753566091404</v>
       </c>
       <c r="E43">
-        <v>-444.732</v>
+        <v>-435.0839999999999</v>
       </c>
       <c r="F43">
-        <v>395.568</v>
+        <v>405.216</v>
       </c>
       <c r="G43">
         <v>159.4</v>
@@ -4813,37 +4813,37 @@
         <v>5.75</v>
       </c>
       <c r="M43">
-        <v>93.27493440000001</v>
+        <v>95.54993280000001</v>
       </c>
       <c r="N43">
-        <v>-87.52493440000001</v>
+        <v>-89.79993280000001</v>
       </c>
       <c r="O43">
-        <v>-21.005984256</v>
+        <v>-21.551983872</v>
       </c>
       <c r="P43">
-        <v>-66.518950144</v>
+        <v>-68.247948928</v>
       </c>
       <c r="Q43">
-        <v>-63.548950144</v>
+        <v>-65.277948928</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08897931866642975</v>
+        <v>0.08972378967791993</v>
       </c>
       <c r="T43">
-        <v>0.8878122388021327</v>
+        <v>0.9031193463676868</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.01479497154167926</v>
+        <v>0.01444271031449642</v>
       </c>
       <c r="W43">
-        <v>0.232311345710472</v>
+        <v>0.2323944089078418</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.06164571475699687</v>
+        <v>0.06017795964373507</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1496454497544871</v>
+        <v>0.1515454497544871</v>
       </c>
       <c r="C44">
-        <v>-93.74064339085959</v>
+        <v>-106.1210841552444</v>
       </c>
       <c r="D44">
-        <v>152.0753566091404</v>
+        <v>149.3429158447556</v>
       </c>
       <c r="E44">
-        <v>-435.084</v>
+        <v>-425.436</v>
       </c>
       <c r="F44">
-        <v>405.216</v>
+        <v>414.864</v>
       </c>
       <c r="G44">
         <v>159.4</v>
@@ -4895,37 +4895,37 @@
         <v>5.75</v>
       </c>
       <c r="M44">
-        <v>95.54993279999999</v>
+        <v>97.82493119999999</v>
       </c>
       <c r="N44">
-        <v>-89.79993279999999</v>
+        <v>-92.07493119999999</v>
       </c>
       <c r="O44">
-        <v>-21.551983872</v>
+        <v>-22.097983488</v>
       </c>
       <c r="P44">
-        <v>-68.247948928</v>
+        <v>-69.976947712</v>
       </c>
       <c r="Q44">
-        <v>-65.277948928</v>
+        <v>-67.006947712</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08972378967791991</v>
+        <v>0.09049438247928693</v>
       </c>
       <c r="T44">
-        <v>0.9031193463676865</v>
+        <v>0.9189635454267688</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.01444271031449642</v>
+        <v>0.01410683333043837</v>
       </c>
       <c r="W44">
-        <v>0.2323944089078418</v>
+        <v>0.2324736087006826</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.06017795964373507</v>
+        <v>0.05877847221015986</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1515454497544871</v>
+        <v>0.1534454497544871</v>
       </c>
       <c r="C45">
-        <v>-106.1210841552444</v>
+        <v>-118.4050668256889</v>
       </c>
       <c r="D45">
-        <v>149.3429158447556</v>
+        <v>146.706933174311</v>
       </c>
       <c r="E45">
-        <v>-425.436</v>
+        <v>-415.788</v>
       </c>
       <c r="F45">
-        <v>414.864</v>
+        <v>424.512</v>
       </c>
       <c r="G45">
         <v>159.4</v>
@@ -4977,37 +4977,37 @@
         <v>5.75</v>
       </c>
       <c r="M45">
-        <v>97.82493119999999</v>
+        <v>100.0999296</v>
       </c>
       <c r="N45">
-        <v>-92.07493119999999</v>
+        <v>-94.34992960000001</v>
       </c>
       <c r="O45">
-        <v>-22.097983488</v>
+        <v>-22.643983104</v>
       </c>
       <c r="P45">
-        <v>-69.976947712</v>
+        <v>-71.70594649600001</v>
       </c>
       <c r="Q45">
-        <v>-67.006947712</v>
+        <v>-68.73594649600001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09049438247928693</v>
+        <v>0.09129249645213133</v>
       </c>
       <c r="T45">
-        <v>0.9189635454267688</v>
+        <v>0.9353736087379612</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.01410683333043837</v>
+        <v>0.01378622348201931</v>
       </c>
       <c r="W45">
-        <v>0.2324736087006826</v>
+        <v>0.2325492085029399</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.05877847221015986</v>
+        <v>0.0574425978417471</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1534454497544871</v>
+        <v>0.1553454497544871</v>
       </c>
       <c r="C46">
-        <v>-118.4050668256889</v>
+        <v>-130.597610425226</v>
       </c>
       <c r="D46">
-        <v>146.706933174311</v>
+        <v>144.162389574774</v>
       </c>
       <c r="E46">
-        <v>-415.788</v>
+        <v>-406.14</v>
       </c>
       <c r="F46">
-        <v>424.512</v>
+        <v>434.16</v>
       </c>
       <c r="G46">
         <v>159.4</v>
@@ -5059,37 +5059,37 @@
         <v>5.75</v>
       </c>
       <c r="M46">
-        <v>100.0999296</v>
+        <v>102.374928</v>
       </c>
       <c r="N46">
-        <v>-94.34992960000001</v>
+        <v>-96.624928</v>
       </c>
       <c r="O46">
-        <v>-22.643983104</v>
+        <v>-23.18998272</v>
       </c>
       <c r="P46">
-        <v>-71.70594649600001</v>
+        <v>-73.43494527999999</v>
       </c>
       <c r="Q46">
-        <v>-68.73594649600001</v>
+        <v>-70.46494527999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09129249645213133</v>
+        <v>0.092119632751261</v>
       </c>
       <c r="T46">
-        <v>0.9353736087379612</v>
+        <v>0.9523804016241059</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.01378622348201931</v>
+        <v>0.01347986296019666</v>
       </c>
       <c r="W46">
-        <v>0.2325492085029399</v>
+        <v>0.2326214483139857</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.0574425978417471</v>
+        <v>0.05616609566748609</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1553454497544871</v>
+        <v>0.1572454497544871</v>
       </c>
       <c r="C47">
-        <v>-130.597610425226</v>
+        <v>-142.7033917056236</v>
       </c>
       <c r="D47">
-        <v>144.162389574774</v>
+        <v>141.7046082943764</v>
       </c>
       <c r="E47">
-        <v>-406.14</v>
+        <v>-396.492</v>
       </c>
       <c r="F47">
-        <v>434.16</v>
+        <v>443.808</v>
       </c>
       <c r="G47">
         <v>159.4</v>
@@ -5141,37 +5141,37 @@
         <v>5.75</v>
       </c>
       <c r="M47">
-        <v>102.374928</v>
+        <v>104.6499264</v>
       </c>
       <c r="N47">
-        <v>-96.624928</v>
+        <v>-98.8999264</v>
       </c>
       <c r="O47">
-        <v>-23.18998272</v>
+        <v>-23.735982336</v>
       </c>
       <c r="P47">
-        <v>-73.43494527999999</v>
+        <v>-75.16394406399999</v>
       </c>
       <c r="Q47">
-        <v>-70.46494527999999</v>
+        <v>-72.19394406399999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.092119632751261</v>
+        <v>0.0929774037281362</v>
       </c>
       <c r="T47">
-        <v>0.9523804016241059</v>
+        <v>0.970017075728256</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.01347986296019666</v>
+        <v>0.01318682246106195</v>
       </c>
       <c r="W47">
-        <v>0.2326214483139857</v>
+        <v>0.2326905472636816</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.05616609566748609</v>
+        <v>0.05494509358775812</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1572454497544871</v>
+        <v>0.1591454497544871</v>
       </c>
       <c r="C48">
-        <v>-142.7033917056236</v>
+        <v>-154.7267738347034</v>
       </c>
       <c r="D48">
-        <v>141.7046082943764</v>
+        <v>139.3292261652966</v>
       </c>
       <c r="E48">
-        <v>-396.492</v>
+        <v>-386.8439999999999</v>
       </c>
       <c r="F48">
-        <v>443.808</v>
+        <v>453.456</v>
       </c>
       <c r="G48">
         <v>159.4</v>
@@ -5223,37 +5223,37 @@
         <v>5.75</v>
       </c>
       <c r="M48">
-        <v>104.6499264</v>
+        <v>106.9249248</v>
       </c>
       <c r="N48">
-        <v>-98.8999264</v>
+        <v>-101.1749248</v>
       </c>
       <c r="O48">
-        <v>-23.735982336</v>
+        <v>-24.281981952</v>
       </c>
       <c r="P48">
-        <v>-75.16394406399999</v>
+        <v>-76.89294284800002</v>
       </c>
       <c r="Q48">
-        <v>-72.19394406399999</v>
+        <v>-73.92294284800002</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.0929774037281362</v>
+        <v>0.09386754342111991</v>
       </c>
       <c r="T48">
-        <v>0.970017075728256</v>
+        <v>0.9883192847042608</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.01318682246106195</v>
+        <v>0.01290625177040106</v>
       </c>
       <c r="W48">
-        <v>0.2326905472636816</v>
+        <v>0.2327567058325394</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.05494509358775812</v>
+        <v>0.05377604904333777</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1591454497544871</v>
+        <v>0.1610454497544871</v>
       </c>
       <c r="C49">
-        <v>-154.7267738347034</v>
+        <v>-166.6718322459294</v>
       </c>
       <c r="D49">
-        <v>139.3292261652966</v>
+        <v>137.0321677540706</v>
       </c>
       <c r="E49">
-        <v>-386.8439999999999</v>
+        <v>-377.1959999999999</v>
       </c>
       <c r="F49">
-        <v>453.456</v>
+        <v>463.104</v>
       </c>
       <c r="G49">
         <v>159.4</v>
@@ -5305,37 +5305,37 @@
         <v>5.75</v>
       </c>
       <c r="M49">
-        <v>106.9249248</v>
+        <v>109.1999232</v>
       </c>
       <c r="N49">
-        <v>-101.1749248</v>
+        <v>-103.4499232</v>
       </c>
       <c r="O49">
-        <v>-24.281981952</v>
+        <v>-24.827981568</v>
       </c>
       <c r="P49">
-        <v>-76.89294284800002</v>
+        <v>-78.62194163200002</v>
       </c>
       <c r="Q49">
-        <v>-73.92294284800002</v>
+        <v>-75.65194163200002</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09386754342111991</v>
+        <v>0.09479191925614144</v>
       </c>
       <c r="T49">
-        <v>0.9883192847042608</v>
+        <v>1.007325424794727</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.01290625177040106</v>
+        <v>0.01263737152518437</v>
       </c>
       <c r="W49">
-        <v>0.2327567058325394</v>
+        <v>0.2328201077943615</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.05377604904333777</v>
+        <v>0.05265571468826824</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1610454497544871</v>
+        <v>0.1629454497544871</v>
       </c>
       <c r="C50">
-        <v>-166.6718322459294</v>
+        <v>-178.5423779724462</v>
       </c>
       <c r="D50">
-        <v>137.0321677540706</v>
+        <v>134.8096220275538</v>
       </c>
       <c r="E50">
-        <v>-377.196</v>
+        <v>-367.548</v>
       </c>
       <c r="F50">
-        <v>463.104</v>
+        <v>472.752</v>
       </c>
       <c r="G50">
         <v>159.4</v>
@@ -5387,37 +5387,37 @@
         <v>5.75</v>
       </c>
       <c r="M50">
-        <v>109.1999232</v>
+        <v>111.4749216</v>
       </c>
       <c r="N50">
-        <v>-103.4499232</v>
+        <v>-105.7249216</v>
       </c>
       <c r="O50">
-        <v>-24.827981568</v>
+        <v>-25.37398118399999</v>
       </c>
       <c r="P50">
-        <v>-78.621941632</v>
+        <v>-80.35094041599999</v>
       </c>
       <c r="Q50">
-        <v>-75.651941632</v>
+        <v>-77.38094041599999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09479191925614144</v>
+        <v>0.09575254512390892</v>
       </c>
       <c r="T50">
-        <v>1.007325424794727</v>
+        <v>1.027076903712271</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.01263737152518437</v>
+        <v>0.01237946598385408</v>
       </c>
       <c r="W50">
-        <v>0.2328201077943615</v>
+        <v>0.2328809219210072</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.05265571468826824</v>
+        <v>0.05158110826605866</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1629454497544871</v>
+        <v>0.1648454497544871</v>
       </c>
       <c r="C51">
-        <v>-178.5423779724462</v>
+        <v>-190.3419787466094</v>
       </c>
       <c r="D51">
-        <v>134.8096220275538</v>
+        <v>132.6580212533906</v>
       </c>
       <c r="E51">
-        <v>-367.548</v>
+        <v>-357.9</v>
       </c>
       <c r="F51">
-        <v>472.752</v>
+        <v>482.4</v>
       </c>
       <c r="G51">
         <v>159.4</v>
@@ -5469,37 +5469,37 @@
         <v>5.75</v>
       </c>
       <c r="M51">
-        <v>111.4749216</v>
+        <v>113.74992</v>
       </c>
       <c r="N51">
-        <v>-105.7249216</v>
+        <v>-107.99992</v>
       </c>
       <c r="O51">
-        <v>-25.37398118399999</v>
+        <v>-25.9199808</v>
       </c>
       <c r="P51">
-        <v>-80.35094041599999</v>
+        <v>-82.0799392</v>
       </c>
       <c r="Q51">
-        <v>-77.38094041599999</v>
+        <v>-79.1099392</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09575254512390892</v>
+        <v>0.09675159602638711</v>
       </c>
       <c r="T51">
-        <v>1.027076903712271</v>
+        <v>1.047618441786517</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.01237946598385408</v>
+        <v>0.01213187666417699</v>
       </c>
       <c r="W51">
-        <v>0.2328809219210072</v>
+        <v>0.2329393034825871</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.05158110826605866</v>
+        <v>0.05054948610073751</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1648454497544871</v>
+        <v>0.1667454497544871</v>
       </c>
       <c r="C52">
-        <v>-190.3419787466094</v>
+        <v>-202.0739781107285</v>
       </c>
       <c r="D52">
-        <v>132.6580212533906</v>
+        <v>130.5740218892715</v>
       </c>
       <c r="E52">
-        <v>-357.9</v>
+        <v>-348.252</v>
       </c>
       <c r="F52">
-        <v>482.4</v>
+        <v>492.048</v>
       </c>
       <c r="G52">
         <v>159.4</v>
@@ -5551,37 +5551,37 @@
         <v>5.75</v>
       </c>
       <c r="M52">
-        <v>113.74992</v>
+        <v>116.0249184</v>
       </c>
       <c r="N52">
-        <v>-107.99992</v>
+        <v>-110.2749184</v>
       </c>
       <c r="O52">
-        <v>-25.9199808</v>
+        <v>-26.465980416</v>
       </c>
       <c r="P52">
-        <v>-82.0799392</v>
+        <v>-83.80893798400001</v>
       </c>
       <c r="Q52">
-        <v>-79.1099392</v>
+        <v>-80.83893798400001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09675159602638711</v>
+        <v>0.09779142451672154</v>
       </c>
       <c r="T52">
-        <v>1.047618441786517</v>
+        <v>1.068998409986242</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.01213187666417699</v>
+        <v>0.01189399672958529</v>
       </c>
       <c r="W52">
-        <v>0.2329393034825871</v>
+        <v>0.2329953955711638</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.05054948610073751</v>
+        <v>0.0495583197066054</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1667454497544871</v>
+        <v>0.1686454497544871</v>
       </c>
       <c r="C53">
-        <v>-202.0739781107285</v>
+        <v>-213.7415127543431</v>
       </c>
       <c r="D53">
-        <v>130.5740218892715</v>
+        <v>128.5544872456569</v>
       </c>
       <c r="E53">
-        <v>-348.252</v>
+        <v>-338.604</v>
       </c>
       <c r="F53">
-        <v>492.048</v>
+        <v>501.696</v>
       </c>
       <c r="G53">
         <v>159.4</v>
@@ -5633,37 +5633,37 @@
         <v>5.75</v>
       </c>
       <c r="M53">
-        <v>116.0249184</v>
+        <v>118.2999168</v>
       </c>
       <c r="N53">
-        <v>-110.2749184</v>
+        <v>-112.5499168</v>
       </c>
       <c r="O53">
-        <v>-26.465980416</v>
+        <v>-27.011980032</v>
       </c>
       <c r="P53">
-        <v>-83.80893798400001</v>
+        <v>-85.53793676799999</v>
       </c>
       <c r="Q53">
-        <v>-80.83893798400001</v>
+        <v>-82.567936768</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09779142451672154</v>
+        <v>0.09887457919415324</v>
       </c>
       <c r="T53">
-        <v>1.068998409986242</v>
+        <v>1.091269210194288</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.01189399672958529</v>
+        <v>0.01166526602324711</v>
       </c>
       <c r="W53">
-        <v>0.2329953955711638</v>
+        <v>0.2330493302717183</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.0495583197066054</v>
+        <v>0.04860527509686297</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1686454497544871</v>
+        <v>0.1705454497544871</v>
       </c>
       <c r="C54">
-        <v>-213.7415127543431</v>
+        <v>-225.3475282671131</v>
       </c>
       <c r="D54">
-        <v>128.5544872456569</v>
+        <v>126.5964717328869</v>
       </c>
       <c r="E54">
-        <v>-338.604</v>
+        <v>-328.956</v>
       </c>
       <c r="F54">
-        <v>501.696</v>
+        <v>511.344</v>
       </c>
       <c r="G54">
         <v>159.4</v>
@@ -5715,37 +5715,37 @@
         <v>5.75</v>
       </c>
       <c r="M54">
-        <v>118.2999168</v>
+        <v>120.5749152</v>
       </c>
       <c r="N54">
-        <v>-112.5499168</v>
+        <v>-114.8249152</v>
       </c>
       <c r="O54">
-        <v>-27.011980032</v>
+        <v>-27.557979648</v>
       </c>
       <c r="P54">
-        <v>-85.53793676799999</v>
+        <v>-87.26693555200001</v>
       </c>
       <c r="Q54">
-        <v>-82.567936768</v>
+        <v>-84.29693555200001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09887457919415324</v>
+        <v>0.1000038255599863</v>
       </c>
       <c r="T54">
-        <v>1.091269210194288</v>
+        <v>1.114487704028209</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.01166526602324711</v>
+        <v>0.01144516666431792</v>
       </c>
       <c r="W54">
-        <v>0.2330493302717183</v>
+        <v>0.2331012297005538</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.04860527509686297</v>
+        <v>0.04768819443465799</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1705454497544871</v>
+        <v>0.1724454497544871</v>
       </c>
       <c r="C55">
-        <v>-225.3475282671131</v>
+        <v>-236.8947934737097</v>
       </c>
       <c r="D55">
-        <v>126.5964717328869</v>
+        <v>124.6972065262902</v>
       </c>
       <c r="E55">
-        <v>-328.956</v>
+        <v>-319.308</v>
       </c>
       <c r="F55">
-        <v>511.344</v>
+        <v>520.992</v>
       </c>
       <c r="G55">
         <v>159.4</v>
@@ -5797,37 +5797,37 @@
         <v>5.75</v>
       </c>
       <c r="M55">
-        <v>120.5749152</v>
+        <v>122.8499136</v>
       </c>
       <c r="N55">
-        <v>-114.8249152</v>
+        <v>-117.0999136</v>
       </c>
       <c r="O55">
-        <v>-27.557979648</v>
+        <v>-28.103979264</v>
       </c>
       <c r="P55">
-        <v>-87.26693555200001</v>
+        <v>-88.995934336</v>
       </c>
       <c r="Q55">
-        <v>-84.29693555200001</v>
+        <v>-86.02593433600001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1000038255599863</v>
+        <v>0.101182169593899</v>
       </c>
       <c r="T55">
-        <v>1.114487704028209</v>
+        <v>1.13871569759404</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.01144516666431792</v>
+        <v>0.01123321913349722</v>
       </c>
       <c r="W55">
-        <v>0.2331012297005538</v>
+        <v>0.2331512069283214</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.04768819443465799</v>
+        <v>0.04680507972290504</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1724454497544871</v>
+        <v>0.1743454497544871</v>
       </c>
       <c r="C56">
-        <v>-236.8947934737097</v>
+        <v>-248.3859134974247</v>
       </c>
       <c r="D56">
-        <v>124.6972065262902</v>
+        <v>122.8540865025753</v>
       </c>
       <c r="E56">
-        <v>-319.308</v>
+        <v>-309.66</v>
       </c>
       <c r="F56">
-        <v>520.992</v>
+        <v>530.64</v>
       </c>
       <c r="G56">
         <v>159.4</v>
@@ -5879,37 +5879,37 @@
         <v>5.75</v>
       </c>
       <c r="M56">
-        <v>122.8499136</v>
+        <v>125.124912</v>
       </c>
       <c r="N56">
-        <v>-117.0999136</v>
+        <v>-119.374912</v>
       </c>
       <c r="O56">
-        <v>-28.103979264</v>
+        <v>-28.64997888</v>
       </c>
       <c r="P56">
-        <v>-88.995934336</v>
+        <v>-90.72493312</v>
       </c>
       <c r="Q56">
-        <v>-86.02593433600001</v>
+        <v>-87.75493312</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.101182169593899</v>
+        <v>0.1024128844737635</v>
       </c>
       <c r="T56">
-        <v>1.13871569759404</v>
+        <v>1.164020490873907</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.01123321913349722</v>
+        <v>0.01102897878561545</v>
       </c>
       <c r="W56">
-        <v>0.2331512069283214</v>
+        <v>0.2331993668023519</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.04680507972290504</v>
+        <v>0.0459540782733977</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1743454497544871</v>
+        <v>0.1762454497544871</v>
       </c>
       <c r="C57">
-        <v>-248.3859134974247</v>
+        <v>-259.8233416821121</v>
       </c>
       <c r="D57">
-        <v>122.8540865025753</v>
+        <v>121.0646583178879</v>
       </c>
       <c r="E57">
-        <v>-309.66</v>
+        <v>-300.0119999999999</v>
       </c>
       <c r="F57">
-        <v>530.64</v>
+        <v>540.288</v>
       </c>
       <c r="G57">
         <v>159.4</v>
@@ -5961,37 +5961,37 @@
         <v>5.75</v>
       </c>
       <c r="M57">
-        <v>125.124912</v>
+        <v>127.3999104</v>
       </c>
       <c r="N57">
-        <v>-119.374912</v>
+        <v>-121.6499104</v>
       </c>
       <c r="O57">
-        <v>-28.64997888</v>
+        <v>-29.195978496</v>
       </c>
       <c r="P57">
-        <v>-90.72493312</v>
+        <v>-92.453931904</v>
       </c>
       <c r="Q57">
-        <v>-87.75493312</v>
+        <v>-89.483931904</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1024128844737635</v>
+        <v>0.1036995409390763</v>
       </c>
       <c r="T57">
-        <v>1.164020490873907</v>
+        <v>1.190475502030133</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.01102897878561545</v>
+        <v>0.01083203273587231</v>
       </c>
       <c r="W57">
-        <v>0.2331993668023519</v>
+        <v>0.2332458066808813</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.0459540782733977</v>
+        <v>0.0451334697328013</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1762454497544871</v>
+        <v>0.1781454497544871</v>
       </c>
       <c r="C58">
-        <v>-259.8233416821121</v>
+        <v>-271.2093904871953</v>
       </c>
       <c r="D58">
-        <v>121.0646583178879</v>
+        <v>119.3266095128047</v>
       </c>
       <c r="E58">
-        <v>-300.0119999999999</v>
+        <v>-290.3639999999999</v>
       </c>
       <c r="F58">
-        <v>540.288</v>
+        <v>549.936</v>
       </c>
       <c r="G58">
         <v>159.4</v>
@@ -6043,37 +6043,37 @@
         <v>5.75</v>
       </c>
       <c r="M58">
-        <v>127.3999104</v>
+        <v>129.6749088</v>
       </c>
       <c r="N58">
-        <v>-121.6499104</v>
+        <v>-123.9249088</v>
       </c>
       <c r="O58">
-        <v>-29.195978496</v>
+        <v>-29.74197811200001</v>
       </c>
       <c r="P58">
-        <v>-92.453931904</v>
+        <v>-94.18293068800003</v>
       </c>
       <c r="Q58">
-        <v>-89.483931904</v>
+        <v>-91.21293068800003</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1036995409390763</v>
+        <v>0.1050460418911478</v>
       </c>
       <c r="T58">
-        <v>1.190475502030133</v>
+        <v>1.218160978821531</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.01083203273587231</v>
+        <v>0.01064199707383947</v>
       </c>
       <c r="W58">
-        <v>0.2332458066808813</v>
+        <v>0.2332906170899887</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.0451334697328013</v>
+        <v>0.04434165447433114</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1781454497544871</v>
+        <v>0.1800454497544871</v>
       </c>
       <c r="C59">
-        <v>-271.2093904871953</v>
+        <v>-282.5462414574812</v>
       </c>
       <c r="D59">
-        <v>119.3266095128047</v>
+        <v>117.6377585425188</v>
       </c>
       <c r="E59">
-        <v>-290.3639999999999</v>
+        <v>-280.7159999999999</v>
       </c>
       <c r="F59">
-        <v>549.936</v>
+        <v>559.5840000000001</v>
       </c>
       <c r="G59">
         <v>159.4</v>
@@ -6125,37 +6125,37 @@
         <v>5.75</v>
       </c>
       <c r="M59">
-        <v>129.6749088</v>
+        <v>131.9499072</v>
       </c>
       <c r="N59">
-        <v>-123.9249088</v>
+        <v>-126.1999072</v>
       </c>
       <c r="O59">
-        <v>-29.74197811200001</v>
+        <v>-30.287977728</v>
       </c>
       <c r="P59">
-        <v>-94.18293068800003</v>
+        <v>-95.91192947200001</v>
       </c>
       <c r="Q59">
-        <v>-91.21293068800003</v>
+        <v>-92.94192947200001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1050460418911478</v>
+        <v>0.1064566619361751</v>
       </c>
       <c r="T59">
-        <v>1.218160978821531</v>
+        <v>1.247164811650615</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.01064199707383947</v>
+        <v>0.01045851436566982</v>
       </c>
       <c r="W59">
-        <v>0.2332906170899887</v>
+        <v>0.2333338823125751</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.04434165447433114</v>
+        <v>0.04357714319029093</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1800454497544871</v>
+        <v>0.1819454497544871</v>
       </c>
       <c r="C60">
-        <v>-282.5462414574811</v>
+        <v>-293.8359543581608</v>
       </c>
       <c r="D60">
-        <v>117.6377585425188</v>
+        <v>115.9960456418391</v>
       </c>
       <c r="E60">
-        <v>-280.716</v>
+        <v>-271.068</v>
       </c>
       <c r="F60">
-        <v>559.5839999999999</v>
+        <v>569.232</v>
       </c>
       <c r="G60">
         <v>159.4</v>
@@ -6207,37 +6207,37 @@
         <v>5.75</v>
       </c>
       <c r="M60">
-        <v>131.9499072</v>
+        <v>134.2249056</v>
       </c>
       <c r="N60">
-        <v>-126.1999072</v>
+        <v>-128.4749056</v>
       </c>
       <c r="O60">
-        <v>-30.28797772799999</v>
+        <v>-30.833977344</v>
       </c>
       <c r="P60">
-        <v>-95.911929472</v>
+        <v>-97.640928256</v>
       </c>
       <c r="Q60">
-        <v>-92.941929472</v>
+        <v>-94.670928256</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1064566619361751</v>
+        <v>0.1079360927151062</v>
       </c>
       <c r="T60">
-        <v>1.247164811650615</v>
+        <v>1.277583465593313</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.01045851436566982</v>
+        <v>0.01028125141031949</v>
       </c>
       <c r="W60">
-        <v>0.2333338823125751</v>
+        <v>0.2333756809174467</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.04357714319029093</v>
+        <v>0.04283854754299787</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1819454497544871</v>
+        <v>0.1838454497544871</v>
       </c>
       <c r="C61">
-        <v>-293.8359543581608</v>
+        <v>-305.0804755554293</v>
       </c>
       <c r="D61">
-        <v>115.9960456418391</v>
+        <v>114.3995244445707</v>
       </c>
       <c r="E61">
-        <v>-271.068</v>
+        <v>-261.42</v>
       </c>
       <c r="F61">
-        <v>569.232</v>
+        <v>578.88</v>
       </c>
       <c r="G61">
         <v>159.4</v>
@@ -6289,37 +6289,37 @@
         <v>5.75</v>
       </c>
       <c r="M61">
-        <v>134.2249056</v>
+        <v>136.499904</v>
       </c>
       <c r="N61">
-        <v>-128.4749056</v>
+        <v>-130.749904</v>
       </c>
       <c r="O61">
-        <v>-30.833977344</v>
+        <v>-31.37997696</v>
       </c>
       <c r="P61">
-        <v>-97.640928256</v>
+        <v>-99.36992704000001</v>
       </c>
       <c r="Q61">
-        <v>-94.670928256</v>
+        <v>-96.39992704000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1079360927151062</v>
+        <v>0.1094894950329839</v>
       </c>
       <c r="T61">
-        <v>1.277583465593313</v>
+        <v>1.309523052233146</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.01028125141031949</v>
+        <v>0.0101098972201475</v>
       </c>
       <c r="W61">
-        <v>0.2333756809174467</v>
+        <v>0.2334160862354892</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.04283854754299787</v>
+        <v>0.04212457175061457</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1838454497544871</v>
+        <v>0.1857454497544871</v>
       </c>
       <c r="C62">
-        <v>-305.0804755554293</v>
+        <v>-316.2816457144163</v>
       </c>
       <c r="D62">
-        <v>114.3995244445707</v>
+        <v>112.8463542855836</v>
       </c>
       <c r="E62">
-        <v>-261.42</v>
+        <v>-251.772</v>
       </c>
       <c r="F62">
-        <v>578.88</v>
+        <v>588.5279999999999</v>
       </c>
       <c r="G62">
         <v>159.4</v>
@@ -6371,37 +6371,37 @@
         <v>5.75</v>
       </c>
       <c r="M62">
-        <v>136.499904</v>
+        <v>138.7749024</v>
       </c>
       <c r="N62">
-        <v>-130.749904</v>
+        <v>-133.0249024</v>
       </c>
       <c r="O62">
-        <v>-31.37997696</v>
+        <v>-31.92597657599999</v>
       </c>
       <c r="P62">
-        <v>-99.36992704000001</v>
+        <v>-101.098925824</v>
       </c>
       <c r="Q62">
-        <v>-96.39992704000001</v>
+        <v>-98.12892582399998</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1094894950329839</v>
+        <v>0.1111225590081886</v>
       </c>
       <c r="T62">
-        <v>1.309523052233146</v>
+        <v>1.34310056639297</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.0101098972201475</v>
+        <v>0.009944161200145079</v>
       </c>
       <c r="W62">
-        <v>0.2334160862354892</v>
+        <v>0.2334551667890058</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.04212457175061457</v>
+        <v>0.04143400500060446</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1857454497544871</v>
+        <v>0.1876454497544871</v>
       </c>
       <c r="C63">
-        <v>-316.2816457144163</v>
+        <v>-327.4412068784418</v>
       </c>
       <c r="D63">
-        <v>112.8463542855836</v>
+        <v>111.3347931215582</v>
       </c>
       <c r="E63">
-        <v>-251.772</v>
+        <v>-242.124</v>
       </c>
       <c r="F63">
-        <v>588.5279999999999</v>
+        <v>598.1759999999999</v>
       </c>
       <c r="G63">
         <v>159.4</v>
@@ -6453,37 +6453,37 @@
         <v>5.75</v>
       </c>
       <c r="M63">
-        <v>138.7749024</v>
+        <v>141.0499008</v>
       </c>
       <c r="N63">
-        <v>-133.0249024</v>
+        <v>-135.2999008</v>
       </c>
       <c r="O63">
-        <v>-31.92597657599999</v>
+        <v>-32.471976192</v>
       </c>
       <c r="P63">
-        <v>-101.098925824</v>
+        <v>-102.827924608</v>
       </c>
       <c r="Q63">
-        <v>-98.12892582399998</v>
+        <v>-99.85792460799999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1111225590081886</v>
+        <v>0.1128415737189304</v>
       </c>
       <c r="T63">
-        <v>1.34310056639297</v>
+        <v>1.378445318140153</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.009944161200145079</v>
+        <v>0.009783771503368543</v>
       </c>
       <c r="W63">
-        <v>0.2334551667890058</v>
+        <v>0.2334929866795057</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.04143400500060446</v>
+        <v>0.04076571459736889</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1876454497544871</v>
+        <v>0.1895454497544871</v>
       </c>
       <c r="C64">
-        <v>-327.4412068784418</v>
+        <v>-338.5608089868373</v>
       </c>
       <c r="D64">
-        <v>111.3347931215582</v>
+        <v>109.8631910131626</v>
       </c>
       <c r="E64">
-        <v>-242.124</v>
+        <v>-232.476</v>
       </c>
       <c r="F64">
-        <v>598.1759999999999</v>
+        <v>607.824</v>
       </c>
       <c r="G64">
         <v>159.4</v>
@@ -6535,37 +6535,37 @@
         <v>5.75</v>
       </c>
       <c r="M64">
-        <v>141.0499008</v>
+        <v>143.3248992</v>
       </c>
       <c r="N64">
-        <v>-135.2999008</v>
+        <v>-137.5748992</v>
       </c>
       <c r="O64">
-        <v>-32.471976192</v>
+        <v>-33.017975808</v>
       </c>
       <c r="P64">
-        <v>-102.827924608</v>
+        <v>-104.556923392</v>
       </c>
       <c r="Q64">
-        <v>-99.85792460799999</v>
+        <v>-101.586923392</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1128415737189304</v>
+        <v>0.1146535081437663</v>
       </c>
       <c r="T64">
-        <v>1.378445318140153</v>
+        <v>1.415700597008806</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.009783771503368543</v>
+        <v>0.009628473542997614</v>
       </c>
       <c r="W64">
-        <v>0.2334929866795057</v>
+        <v>0.2335296059385612</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.04076571459736889</v>
+        <v>0.04011863976249008</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1895454497544871</v>
+        <v>0.1914454497544871</v>
       </c>
       <c r="C65">
-        <v>-338.5608089868373</v>
+        <v>-349.6420158826029</v>
       </c>
       <c r="D65">
-        <v>109.8631910131626</v>
+        <v>108.4299841173971</v>
       </c>
       <c r="E65">
-        <v>-232.476</v>
+        <v>-222.828</v>
       </c>
       <c r="F65">
-        <v>607.824</v>
+        <v>617.472</v>
       </c>
       <c r="G65">
         <v>159.4</v>
@@ -6617,37 +6617,37 @@
         <v>5.75</v>
       </c>
       <c r="M65">
-        <v>143.3248992</v>
+        <v>145.5998976</v>
       </c>
       <c r="N65">
-        <v>-137.5748992</v>
+        <v>-139.8498976</v>
       </c>
       <c r="O65">
-        <v>-33.017975808</v>
+        <v>-33.563975424</v>
       </c>
       <c r="P65">
-        <v>-104.556923392</v>
+        <v>-106.285922176</v>
       </c>
       <c r="Q65">
-        <v>-101.586923392</v>
+        <v>-103.315922176</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1146535081437663</v>
+        <v>0.1165661055922043</v>
       </c>
       <c r="T65">
-        <v>1.415700597008806</v>
+        <v>1.455025613592384</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.009628473542997614</v>
+        <v>0.009478028643888277</v>
       </c>
       <c r="W65">
-        <v>0.2335296059385612</v>
+        <v>0.2335650808457712</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.04011863976249008</v>
+        <v>0.03949178601620118</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1914454497544871</v>
+        <v>0.1933454497544871</v>
       </c>
       <c r="C66">
-        <v>-349.6420158826029</v>
+        <v>-360.6863108558865</v>
       </c>
       <c r="D66">
-        <v>108.4299841173971</v>
+        <v>107.0336891441135</v>
       </c>
       <c r="E66">
-        <v>-222.828</v>
+        <v>-213.1799999999999</v>
       </c>
       <c r="F66">
-        <v>617.472</v>
+        <v>627.12</v>
       </c>
       <c r="G66">
         <v>159.4</v>
@@ -6699,37 +6699,37 @@
         <v>5.75</v>
       </c>
       <c r="M66">
-        <v>145.5998976</v>
+        <v>147.874896</v>
       </c>
       <c r="N66">
-        <v>-139.8498976</v>
+        <v>-142.124896</v>
       </c>
       <c r="O66">
-        <v>-33.563975424</v>
+        <v>-34.10997504</v>
       </c>
       <c r="P66">
-        <v>-106.285922176</v>
+        <v>-108.01492096</v>
       </c>
       <c r="Q66">
-        <v>-103.315922176</v>
+        <v>-105.04492096</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1165661055922043</v>
+        <v>0.1185879943234102</v>
       </c>
       <c r="T66">
-        <v>1.455025613592384</v>
+        <v>1.496597773980738</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.009478028643888277</v>
+        <v>0.009332212818597687</v>
       </c>
       <c r="W66">
-        <v>0.2335650808457712</v>
+        <v>0.2335994642173747</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.03949178601620118</v>
+        <v>0.03888422007749037</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1933454497544871</v>
+        <v>0.1952454497544871</v>
       </c>
       <c r="C67">
-        <v>-360.6863108558865</v>
+        <v>-371.6951017645954</v>
       </c>
       <c r="D67">
-        <v>107.0336891441135</v>
+        <v>105.6728982354046</v>
       </c>
       <c r="E67">
-        <v>-213.1799999999999</v>
+        <v>-203.5319999999999</v>
       </c>
       <c r="F67">
-        <v>627.12</v>
+        <v>636.768</v>
       </c>
       <c r="G67">
         <v>159.4</v>
@@ -6781,37 +6781,37 @@
         <v>5.75</v>
       </c>
       <c r="M67">
-        <v>147.874896</v>
+        <v>150.1498944</v>
       </c>
       <c r="N67">
-        <v>-142.124896</v>
+        <v>-144.3998944</v>
       </c>
       <c r="O67">
-        <v>-34.10997504</v>
+        <v>-34.65597465600001</v>
       </c>
       <c r="P67">
-        <v>-108.01492096</v>
+        <v>-109.743919744</v>
       </c>
       <c r="Q67">
-        <v>-105.04492096</v>
+        <v>-106.773919744</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1185879943234102</v>
+        <v>0.1207288176858634</v>
       </c>
       <c r="T67">
-        <v>1.496597773980738</v>
+        <v>1.540615355568407</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.009332212818597687</v>
+        <v>0.009190815654679539</v>
       </c>
       <c r="W67">
-        <v>0.2335994642173747</v>
+        <v>0.2336328056686266</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.03888422007749037</v>
+        <v>0.03829506522783144</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1952454497544871</v>
+        <v>0.1971454497544871</v>
       </c>
       <c r="C68">
-        <v>-371.6951017645954</v>
+        <v>-382.669725769301</v>
       </c>
       <c r="D68">
-        <v>105.6728982354046</v>
+        <v>104.346274230699</v>
       </c>
       <c r="E68">
-        <v>-203.5319999999999</v>
+        <v>-193.8839999999999</v>
       </c>
       <c r="F68">
-        <v>636.768</v>
+        <v>646.4160000000001</v>
       </c>
       <c r="G68">
         <v>159.4</v>
@@ -6863,37 +6863,37 @@
         <v>5.75</v>
       </c>
       <c r="M68">
-        <v>150.1498944</v>
+        <v>152.4248928</v>
       </c>
       <c r="N68">
-        <v>-144.3998944</v>
+        <v>-146.6748928</v>
       </c>
       <c r="O68">
-        <v>-34.65597465600001</v>
+        <v>-35.201974272</v>
       </c>
       <c r="P68">
-        <v>-109.743919744</v>
+        <v>-111.472918528</v>
       </c>
       <c r="Q68">
-        <v>-106.773919744</v>
+        <v>-108.502918528</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1207288176858634</v>
+        <v>0.1229993879187684</v>
       </c>
       <c r="T68">
-        <v>1.540615355568407</v>
+        <v>1.58730066937351</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.009190815654679539</v>
+        <v>0.009053639301624622</v>
       </c>
       <c r="W68">
-        <v>0.2336328056686266</v>
+        <v>0.2336651518526769</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.03829506522783144</v>
+        <v>0.03772349709010259</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1971454497544871</v>
+        <v>0.1990454497544871</v>
       </c>
       <c r="C69">
-        <v>-382.669725769301</v>
+        <v>-393.6114537159118</v>
       </c>
       <c r="D69">
-        <v>104.346274230699</v>
+        <v>103.0525462840882</v>
       </c>
       <c r="E69">
-        <v>-193.8839999999999</v>
+        <v>-184.236</v>
       </c>
       <c r="F69">
-        <v>646.4160000000001</v>
+        <v>656.064</v>
       </c>
       <c r="G69">
         <v>159.4</v>
@@ -6945,37 +6945,37 @@
         <v>5.75</v>
       </c>
       <c r="M69">
-        <v>152.4248928</v>
+        <v>154.6998912</v>
       </c>
       <c r="N69">
-        <v>-146.6748928</v>
+        <v>-148.9498912</v>
       </c>
       <c r="O69">
-        <v>-35.201974272</v>
+        <v>-35.747973888</v>
       </c>
       <c r="P69">
-        <v>-111.472918528</v>
+        <v>-113.201917312</v>
       </c>
       <c r="Q69">
-        <v>-108.502918528</v>
+        <v>-110.231917312</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1229993879187684</v>
+        <v>0.1254118687912299</v>
       </c>
       <c r="T69">
-        <v>1.58730066937351</v>
+        <v>1.636903815291432</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.009053639301624622</v>
+        <v>0.008920497547188967</v>
       </c>
       <c r="W69">
-        <v>0.2336651518526769</v>
+        <v>0.2336965466783729</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.03772349709010259</v>
+        <v>0.03716873977995405</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1990454497544871</v>
+        <v>0.2009454497544871</v>
       </c>
       <c r="C70">
-        <v>-393.6114537159118</v>
+        <v>-404.5214941963101</v>
       </c>
       <c r="D70">
-        <v>103.0525462840882</v>
+        <v>101.7905058036899</v>
       </c>
       <c r="E70">
-        <v>-184.236</v>
+        <v>-174.588</v>
       </c>
       <c r="F70">
-        <v>656.064</v>
+        <v>665.712</v>
       </c>
       <c r="G70">
         <v>159.4</v>
@@ -7027,37 +7027,37 @@
         <v>5.75</v>
       </c>
       <c r="M70">
-        <v>154.6998912</v>
+        <v>156.9748896</v>
       </c>
       <c r="N70">
-        <v>-148.9498912</v>
+        <v>-151.2248896</v>
       </c>
       <c r="O70">
-        <v>-35.747973888</v>
+        <v>-36.293973504</v>
       </c>
       <c r="P70">
-        <v>-113.201917312</v>
+        <v>-114.930916096</v>
       </c>
       <c r="Q70">
-        <v>-110.231917312</v>
+        <v>-111.960916096</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1254118687912299</v>
+        <v>0.1279799935909469</v>
       </c>
       <c r="T70">
-        <v>1.636903815291432</v>
+        <v>1.689707164171801</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.008920497547188967</v>
+        <v>0.008791214974041299</v>
       </c>
       <c r="W70">
-        <v>0.2336965466783729</v>
+        <v>0.2337270315091211</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.03716873977995405</v>
+        <v>0.03663006239183875</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2009454497544871</v>
+        <v>0.2028454497544871</v>
       </c>
       <c r="C71">
-        <v>-404.5214941963101</v>
+        <v>-415.4009973142252</v>
       </c>
       <c r="D71">
-        <v>101.7905058036899</v>
+        <v>100.5590026857749</v>
       </c>
       <c r="E71">
-        <v>-174.588</v>
+        <v>-164.9399999999999</v>
       </c>
       <c r="F71">
-        <v>665.712</v>
+        <v>675.36</v>
       </c>
       <c r="G71">
         <v>159.4</v>
@@ -7109,37 +7109,37 @@
         <v>5.75</v>
       </c>
       <c r="M71">
-        <v>156.9748896</v>
+        <v>159.249888</v>
       </c>
       <c r="N71">
-        <v>-151.2248896</v>
+        <v>-153.499888</v>
       </c>
       <c r="O71">
-        <v>-36.293973504</v>
+        <v>-36.83997312</v>
       </c>
       <c r="P71">
-        <v>-114.930916096</v>
+        <v>-116.65991488</v>
       </c>
       <c r="Q71">
-        <v>-111.960916096</v>
+        <v>-113.68991488</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1279799935909469</v>
+        <v>0.1307193267106452</v>
       </c>
       <c r="T71">
-        <v>1.689707164171801</v>
+        <v>1.746030736310861</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.008791214974041299</v>
+        <v>0.008665626188697853</v>
       </c>
       <c r="W71">
-        <v>0.2337270315091211</v>
+        <v>0.2337566453447051</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.03663006239183875</v>
+        <v>0.03610677578624111</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2028454497544871</v>
+        <v>0.2047454497544871</v>
       </c>
       <c r="C72">
-        <v>-415.4009973142252</v>
+        <v>-426.2510581810074</v>
       </c>
       <c r="D72">
-        <v>100.5590026857749</v>
+        <v>99.35694181899265</v>
       </c>
       <c r="E72">
-        <v>-164.9399999999999</v>
+        <v>-155.2919999999999</v>
       </c>
       <c r="F72">
-        <v>675.36</v>
+        <v>685.008</v>
       </c>
       <c r="G72">
         <v>159.4</v>
@@ -7191,37 +7191,37 @@
         <v>5.75</v>
       </c>
       <c r="M72">
-        <v>159.249888</v>
+        <v>161.5248864</v>
       </c>
       <c r="N72">
-        <v>-153.499888</v>
+        <v>-155.7748864</v>
       </c>
       <c r="O72">
-        <v>-36.83997312</v>
+        <v>-37.385972736</v>
       </c>
       <c r="P72">
-        <v>-116.65991488</v>
+        <v>-118.388913664</v>
       </c>
       <c r="Q72">
-        <v>-113.68991488</v>
+        <v>-115.418913664</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1307193267106452</v>
+        <v>0.1336475793558398</v>
       </c>
       <c r="T72">
-        <v>1.746030736310861</v>
+        <v>1.806238692735374</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.008665626188697853</v>
+        <v>0.0085435751156176</v>
       </c>
       <c r="W72">
-        <v>0.2337566453447051</v>
+        <v>0.2337854249877374</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.03610677578624111</v>
+        <v>0.03559822964840664</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2047454497544871</v>
+        <v>0.2066454497544871</v>
       </c>
       <c r="C73">
-        <v>-426.2510581810072</v>
+        <v>-437.0727201636387</v>
       </c>
       <c r="D73">
-        <v>99.35694181899265</v>
+        <v>98.18327983636127</v>
       </c>
       <c r="E73">
-        <v>-155.292</v>
+        <v>-145.644</v>
       </c>
       <c r="F73">
-        <v>685.0079999999999</v>
+        <v>694.6559999999999</v>
       </c>
       <c r="G73">
         <v>159.4</v>
@@ -7273,37 +7273,37 @@
         <v>5.75</v>
       </c>
       <c r="M73">
-        <v>161.5248864</v>
+        <v>163.7998848</v>
       </c>
       <c r="N73">
-        <v>-155.7748864</v>
+        <v>-158.0498848</v>
       </c>
       <c r="O73">
-        <v>-37.38597273599999</v>
+        <v>-37.931972352</v>
       </c>
       <c r="P73">
-        <v>-118.388913664</v>
+        <v>-120.117912448</v>
       </c>
       <c r="Q73">
-        <v>-115.418913664</v>
+        <v>-117.147912448</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1336475793558398</v>
+        <v>0.1367849929042627</v>
       </c>
       <c r="T73">
-        <v>1.806238692735373</v>
+        <v>1.870747217475922</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.008543575115617602</v>
+        <v>0.008424914350122912</v>
       </c>
       <c r="W73">
-        <v>0.2337854249877374</v>
+        <v>0.233813405196241</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.03559822964840664</v>
+        <v>0.03510380979217875</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2066454497544871</v>
+        <v>0.2085454497544871</v>
       </c>
       <c r="C74">
-        <v>-437.0727201636387</v>
+        <v>-447.8669779052253</v>
       </c>
       <c r="D74">
-        <v>98.18327983636127</v>
+        <v>97.03702209477461</v>
       </c>
       <c r="E74">
-        <v>-145.644</v>
+        <v>-135.996</v>
       </c>
       <c r="F74">
-        <v>694.6559999999999</v>
+        <v>704.304</v>
       </c>
       <c r="G74">
         <v>159.4</v>
@@ -7355,37 +7355,37 @@
         <v>5.75</v>
       </c>
       <c r="M74">
-        <v>163.7998848</v>
+        <v>166.0748832</v>
       </c>
       <c r="N74">
-        <v>-158.0498848</v>
+        <v>-160.3248832</v>
       </c>
       <c r="O74">
-        <v>-37.931972352</v>
+        <v>-38.477971968</v>
       </c>
       <c r="P74">
-        <v>-120.117912448</v>
+        <v>-121.846911232</v>
       </c>
       <c r="Q74">
-        <v>-117.147912448</v>
+        <v>-118.876911232</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1367849929042627</v>
+        <v>0.1401548074562724</v>
       </c>
       <c r="T74">
-        <v>1.870747217475922</v>
+        <v>1.940034151456512</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.008424914350122912</v>
+        <v>0.008309504564504791</v>
       </c>
       <c r="W74">
-        <v>0.233813405196241</v>
+        <v>0.2338406188236898</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.03510380979217875</v>
+        <v>0.03462293568543662</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2085454497544871</v>
+        <v>0.2104454497544871</v>
       </c>
       <c r="C75">
-        <v>-447.8669779052253</v>
+        <v>-458.634780136353</v>
       </c>
       <c r="D75">
-        <v>97.03702209477461</v>
+        <v>95.91721986364705</v>
       </c>
       <c r="E75">
-        <v>-135.996</v>
+        <v>-126.348</v>
       </c>
       <c r="F75">
-        <v>704.304</v>
+        <v>713.952</v>
       </c>
       <c r="G75">
         <v>159.4</v>
@@ -7437,37 +7437,37 @@
         <v>5.75</v>
       </c>
       <c r="M75">
-        <v>166.0748832</v>
+        <v>168.3498816</v>
       </c>
       <c r="N75">
-        <v>-160.3248832</v>
+        <v>-162.5998816</v>
       </c>
       <c r="O75">
-        <v>-38.477971968</v>
+        <v>-39.023971584</v>
       </c>
       <c r="P75">
-        <v>-121.846911232</v>
+        <v>-123.575910016</v>
       </c>
       <c r="Q75">
-        <v>-118.876911232</v>
+        <v>-120.605910016</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1401548074562724</v>
+        <v>0.1437838385122829</v>
       </c>
       <c r="T75">
-        <v>1.940034151456512</v>
+        <v>2.014650849589454</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.008309504564504791</v>
+        <v>0.008197213962281753</v>
       </c>
       <c r="W75">
-        <v>0.2338406188236898</v>
+        <v>0.233867096947694</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.03462293568543662</v>
+        <v>0.03415505817617392</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2104454497544871</v>
+        <v>0.2123454497544871</v>
       </c>
       <c r="C76">
-        <v>-458.634780136353</v>
+        <v>-469.3770322940046</v>
       </c>
       <c r="D76">
-        <v>95.91721986364705</v>
+        <v>94.8229677059953</v>
       </c>
       <c r="E76">
-        <v>-126.348</v>
+        <v>-116.7</v>
       </c>
       <c r="F76">
-        <v>713.952</v>
+        <v>723.5999999999999</v>
       </c>
       <c r="G76">
         <v>159.4</v>
@@ -7519,37 +7519,37 @@
         <v>5.75</v>
       </c>
       <c r="M76">
-        <v>168.3498816</v>
+        <v>170.62488</v>
       </c>
       <c r="N76">
-        <v>-162.5998816</v>
+        <v>-164.87488</v>
       </c>
       <c r="O76">
-        <v>-39.023971584</v>
+        <v>-39.5699712</v>
       </c>
       <c r="P76">
-        <v>-123.575910016</v>
+        <v>-125.3049088</v>
       </c>
       <c r="Q76">
-        <v>-120.605910016</v>
+        <v>-122.3349088</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1437838385122829</v>
+        <v>0.1477031920527742</v>
       </c>
       <c r="T76">
-        <v>2.014650849589454</v>
+        <v>2.095236883573033</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.008197213962281753</v>
+        <v>0.008087917776117996</v>
       </c>
       <c r="W76">
-        <v>0.233867096947694</v>
+        <v>0.2338928689883914</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.03415505817617392</v>
+        <v>0.03369965740049163</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2123454497544871</v>
+        <v>0.2142454497544871</v>
       </c>
       <c r="C77">
-        <v>-469.3770322940046</v>
+        <v>-480.0945989632378</v>
       </c>
       <c r="D77">
-        <v>94.8229677059953</v>
+        <v>93.75340103676214</v>
       </c>
       <c r="E77">
-        <v>-116.7</v>
+        <v>-107.052</v>
       </c>
       <c r="F77">
-        <v>723.5999999999999</v>
+        <v>733.2479999999999</v>
       </c>
       <c r="G77">
         <v>159.4</v>
@@ -7601,37 +7601,37 @@
         <v>5.75</v>
       </c>
       <c r="M77">
-        <v>170.62488</v>
+        <v>172.8998784</v>
       </c>
       <c r="N77">
-        <v>-164.87488</v>
+        <v>-167.1498784</v>
       </c>
       <c r="O77">
-        <v>-39.5699712</v>
+        <v>-40.11597081599999</v>
       </c>
       <c r="P77">
-        <v>-125.3049088</v>
+        <v>-127.033907584</v>
       </c>
       <c r="Q77">
-        <v>-122.3349088</v>
+        <v>-124.063907584</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1477031920527742</v>
+        <v>0.1519491583883065</v>
       </c>
       <c r="T77">
-        <v>2.095236883573033</v>
+        <v>2.182538420388576</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.008087917776117996</v>
+        <v>0.007981497805379602</v>
       </c>
       <c r="W77">
-        <v>0.2338928689883914</v>
+        <v>0.2339179628174915</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.03369965740049163</v>
+        <v>0.0332562408557483</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2142454497544871</v>
+        <v>0.2161454497544871</v>
       </c>
       <c r="C78">
-        <v>-480.0945989632378</v>
+        <v>-490.7883061554556</v>
       </c>
       <c r="D78">
-        <v>93.75340103676214</v>
+        <v>92.70769384454432</v>
       </c>
       <c r="E78">
-        <v>-107.052</v>
+        <v>-97.404</v>
       </c>
       <c r="F78">
-        <v>733.2479999999999</v>
+        <v>742.896</v>
       </c>
       <c r="G78">
         <v>159.4</v>
@@ -7683,37 +7683,37 @@
         <v>5.75</v>
       </c>
       <c r="M78">
-        <v>172.8998784</v>
+        <v>175.1748768</v>
       </c>
       <c r="N78">
-        <v>-167.1498784</v>
+        <v>-169.4248768</v>
       </c>
       <c r="O78">
-        <v>-40.11597081599999</v>
+        <v>-40.661970432</v>
       </c>
       <c r="P78">
-        <v>-127.033907584</v>
+        <v>-128.762906368</v>
       </c>
       <c r="Q78">
-        <v>-124.063907584</v>
+        <v>-125.792906368</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1519491583883065</v>
+        <v>0.1565643391877981</v>
       </c>
       <c r="T78">
-        <v>2.182538420388576</v>
+        <v>2.27743139518808</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.007981497805379602</v>
+        <v>0.007877841989725323</v>
       </c>
       <c r="W78">
-        <v>0.2339179628174915</v>
+        <v>0.2339424048588228</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.0332562408557483</v>
+        <v>0.0328243416238555</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2161454497544871</v>
+        <v>0.2180454497544871</v>
       </c>
       <c r="C79">
-        <v>-490.7883061554556</v>
+        <v>-501.458943435893</v>
       </c>
       <c r="D79">
-        <v>92.70769384454432</v>
+        <v>91.68505656410693</v>
       </c>
       <c r="E79">
-        <v>-97.404</v>
+        <v>-87.75599999999997</v>
       </c>
       <c r="F79">
-        <v>742.896</v>
+        <v>752.544</v>
       </c>
       <c r="G79">
         <v>159.4</v>
@@ -7765,37 +7765,37 @@
         <v>5.75</v>
       </c>
       <c r="M79">
-        <v>175.1748768</v>
+        <v>177.4498752</v>
       </c>
       <c r="N79">
-        <v>-169.4248768</v>
+        <v>-171.6998752</v>
       </c>
       <c r="O79">
-        <v>-40.661970432</v>
+        <v>-41.207970048</v>
       </c>
       <c r="P79">
-        <v>-128.762906368</v>
+        <v>-130.491905152</v>
       </c>
       <c r="Q79">
-        <v>-125.792906368</v>
+        <v>-127.521905152</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1565643391877981</v>
+        <v>0.1615990818781525</v>
       </c>
       <c r="T79">
-        <v>2.27743139518808</v>
+        <v>2.380951004060265</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.007877841989725323</v>
+        <v>0.007776844015498072</v>
       </c>
       <c r="W79">
-        <v>0.2339424048588228</v>
+        <v>0.2339662201811456</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.0328243416238555</v>
+        <v>0.03240351673124198</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2180454497544871</v>
+        <v>0.2199454497544871</v>
       </c>
       <c r="C80">
-        <v>-501.458943435893</v>
+        <v>-512.1072659118314</v>
       </c>
       <c r="D80">
-        <v>91.68505656410693</v>
+        <v>90.68473408816863</v>
       </c>
       <c r="E80">
-        <v>-87.75599999999997</v>
+        <v>-78.10799999999995</v>
       </c>
       <c r="F80">
-        <v>752.544</v>
+        <v>762.192</v>
       </c>
       <c r="G80">
         <v>159.4</v>
@@ -7847,37 +7847,37 @@
         <v>5.75</v>
       </c>
       <c r="M80">
-        <v>177.4498752</v>
+        <v>179.7248736</v>
       </c>
       <c r="N80">
-        <v>-171.6998752</v>
+        <v>-173.9748736</v>
       </c>
       <c r="O80">
-        <v>-41.207970048</v>
+        <v>-41.753969664</v>
       </c>
       <c r="P80">
-        <v>-130.491905152</v>
+        <v>-132.220903936</v>
       </c>
       <c r="Q80">
-        <v>-127.521905152</v>
+        <v>-129.250903936</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1615990818781525</v>
+        <v>0.1671133238723503</v>
       </c>
       <c r="T80">
-        <v>2.380951004060265</v>
+        <v>2.49432962330123</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.007776844015498072</v>
+        <v>0.007678402952010755</v>
       </c>
       <c r="W80">
-        <v>0.2339662201811456</v>
+        <v>0.2339894325839159</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.03240351673124198</v>
+        <v>0.03199334563337819</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2199454497544871</v>
+        <v>0.2218454497544871</v>
       </c>
       <c r="C81">
-        <v>-512.1072659118314</v>
+        <v>-522.733996092065</v>
       </c>
       <c r="D81">
-        <v>90.68473408816863</v>
+        <v>89.706003907935</v>
       </c>
       <c r="E81">
-        <v>-78.10799999999995</v>
+        <v>-68.45999999999992</v>
       </c>
       <c r="F81">
-        <v>762.192</v>
+        <v>771.84</v>
       </c>
       <c r="G81">
         <v>159.4</v>
@@ -7929,37 +7929,37 @@
         <v>5.75</v>
       </c>
       <c r="M81">
-        <v>179.7248736</v>
+        <v>181.999872</v>
       </c>
       <c r="N81">
-        <v>-173.9748736</v>
+        <v>-176.249872</v>
       </c>
       <c r="O81">
-        <v>-41.753969664</v>
+        <v>-42.29996928</v>
       </c>
       <c r="P81">
-        <v>-132.220903936</v>
+        <v>-133.94990272</v>
       </c>
       <c r="Q81">
-        <v>-129.250903936</v>
+        <v>-130.97990272</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1671133238723503</v>
+        <v>0.1731789900659678</v>
       </c>
       <c r="T81">
-        <v>2.49432962330123</v>
+        <v>2.619046104466292</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.007678402952010755</v>
+        <v>0.007582422915110621</v>
       </c>
       <c r="W81">
-        <v>0.2339894325839159</v>
+        <v>0.2340120646766169</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.03199334563337819</v>
+        <v>0.0315934288129609</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2218454497544871</v>
+        <v>0.2237454497544871</v>
       </c>
       <c r="C82">
-        <v>-522.733996092065</v>
+        <v>-533.3398256272415</v>
       </c>
       <c r="D82">
-        <v>89.706003907935</v>
+        <v>88.74817437275867</v>
       </c>
       <c r="E82">
-        <v>-68.45999999999992</v>
+        <v>-58.8119999999999</v>
       </c>
       <c r="F82">
-        <v>771.84</v>
+        <v>781.4880000000001</v>
       </c>
       <c r="G82">
         <v>159.4</v>
@@ -8011,37 +8011,37 @@
         <v>5.75</v>
       </c>
       <c r="M82">
-        <v>181.999872</v>
+        <v>184.2748704</v>
       </c>
       <c r="N82">
-        <v>-176.249872</v>
+        <v>-178.5248704</v>
       </c>
       <c r="O82">
-        <v>-42.29996928</v>
+        <v>-42.845968896</v>
       </c>
       <c r="P82">
-        <v>-133.94990272</v>
+        <v>-135.678901504</v>
       </c>
       <c r="Q82">
-        <v>-130.97990272</v>
+        <v>-132.708901504</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1731789900659678</v>
+        <v>0.1798831474378609</v>
       </c>
       <c r="T82">
-        <v>2.619046104466292</v>
+        <v>2.756890636280307</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.007582422915110621</v>
+        <v>0.007488812755664809</v>
       </c>
       <c r="W82">
-        <v>0.2340120646766169</v>
+        <v>0.2340341379522143</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.0315934288129609</v>
+        <v>0.03120338648193666</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2237454497544871</v>
+        <v>0.2256454497544871</v>
       </c>
       <c r="C83">
-        <v>-533.3398256272415</v>
+        <v>-543.9254169398846</v>
       </c>
       <c r="D83">
-        <v>88.74817437275867</v>
+        <v>87.81058306011541</v>
       </c>
       <c r="E83">
-        <v>-58.8119999999999</v>
+        <v>-49.16399999999999</v>
       </c>
       <c r="F83">
-        <v>781.4880000000001</v>
+        <v>791.136</v>
       </c>
       <c r="G83">
         <v>159.4</v>
@@ -8093,37 +8093,37 @@
         <v>5.75</v>
       </c>
       <c r="M83">
-        <v>184.2748704</v>
+        <v>186.5498688</v>
       </c>
       <c r="N83">
-        <v>-178.5248704</v>
+        <v>-180.7998688</v>
       </c>
       <c r="O83">
-        <v>-42.845968896</v>
+        <v>-43.391968512</v>
       </c>
       <c r="P83">
-        <v>-135.678901504</v>
+        <v>-137.407900288</v>
       </c>
       <c r="Q83">
-        <v>-132.708901504</v>
+        <v>-134.437900288</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1798831474378609</v>
+        <v>0.1873322111844087</v>
       </c>
       <c r="T83">
-        <v>2.756890636280307</v>
+        <v>2.910051227184769</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.007488812755664809</v>
+        <v>0.00739748577083963</v>
       </c>
       <c r="W83">
-        <v>0.2340341379522143</v>
+        <v>0.234055672855236</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.03120338648193666</v>
+        <v>0.03082285737849844</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2256454497544871</v>
+        <v>0.2275454497544871</v>
       </c>
       <c r="C84">
-        <v>-543.9254169398846</v>
+        <v>-554.491404752177</v>
       </c>
       <c r="D84">
-        <v>87.81058306011541</v>
+        <v>86.89259524782301</v>
       </c>
       <c r="E84">
-        <v>-49.16399999999999</v>
+        <v>-39.51599999999996</v>
       </c>
       <c r="F84">
-        <v>791.136</v>
+        <v>800.784</v>
       </c>
       <c r="G84">
         <v>159.4</v>
@@ -8175,37 +8175,37 @@
         <v>5.75</v>
       </c>
       <c r="M84">
-        <v>186.5498688</v>
+        <v>188.8248672</v>
       </c>
       <c r="N84">
-        <v>-180.7998688</v>
+        <v>-183.0748672</v>
       </c>
       <c r="O84">
-        <v>-43.391968512</v>
+        <v>-43.937968128</v>
       </c>
       <c r="P84">
-        <v>-137.407900288</v>
+        <v>-139.136899072</v>
       </c>
       <c r="Q84">
-        <v>-134.437900288</v>
+        <v>-136.166899072</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1873322111844087</v>
+        <v>0.1956576353717268</v>
       </c>
       <c r="T84">
-        <v>2.910051227184769</v>
+        <v>3.081230711136814</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.00739748577083963</v>
+        <v>0.007308359436251201</v>
       </c>
       <c r="W84">
-        <v>0.234055672855236</v>
+        <v>0.234076688844932</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.03082285737849844</v>
+        <v>0.03045149765104671</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2275454497544871</v>
+        <v>0.2294454497544871</v>
       </c>
       <c r="C85">
-        <v>-554.491404752177</v>
+        <v>-565.0383975189</v>
       </c>
       <c r="D85">
-        <v>86.89259524782301</v>
+        <v>85.99360248110006</v>
       </c>
       <c r="E85">
-        <v>-39.51599999999996</v>
+        <v>-29.86799999999994</v>
       </c>
       <c r="F85">
-        <v>800.784</v>
+        <v>810.432</v>
       </c>
       <c r="G85">
         <v>159.4</v>
@@ -8257,37 +8257,37 @@
         <v>5.75</v>
       </c>
       <c r="M85">
-        <v>188.8248672</v>
+        <v>191.0998656</v>
       </c>
       <c r="N85">
-        <v>-183.0748672</v>
+        <v>-185.3498656</v>
       </c>
       <c r="O85">
-        <v>-43.937968128</v>
+        <v>-44.483967744</v>
       </c>
       <c r="P85">
-        <v>-139.136899072</v>
+        <v>-140.865897856</v>
       </c>
       <c r="Q85">
-        <v>-136.166899072</v>
+        <v>-137.895897856</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1956576353717268</v>
+        <v>0.2050237375824598</v>
       </c>
       <c r="T85">
-        <v>3.081230711136814</v>
+        <v>3.273807630582866</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.007308359436251201</v>
+        <v>0.007221355157248211</v>
       </c>
       <c r="W85">
-        <v>0.234076688844932</v>
+        <v>0.2340972044539209</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.03045149765104671</v>
+        <v>0.03008897982186753</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2294454497544871</v>
+        <v>0.2313454497544871</v>
       </c>
       <c r="C86">
-        <v>-565.0383975188998</v>
+        <v>-575.5669787723356</v>
       </c>
       <c r="D86">
-        <v>85.99360248110006</v>
+        <v>85.11302122766433</v>
       </c>
       <c r="E86">
-        <v>-29.86800000000005</v>
+        <v>-20.22000000000003</v>
       </c>
       <c r="F86">
-        <v>810.4319999999999</v>
+        <v>820.0799999999999</v>
       </c>
       <c r="G86">
         <v>159.4</v>
@@ -8339,37 +8339,37 @@
         <v>5.75</v>
       </c>
       <c r="M86">
-        <v>191.0998656</v>
+        <v>193.374864</v>
       </c>
       <c r="N86">
-        <v>-185.3498656</v>
+        <v>-187.624864</v>
       </c>
       <c r="O86">
-        <v>-44.483967744</v>
+        <v>-45.02996736</v>
       </c>
       <c r="P86">
-        <v>-140.865897856</v>
+        <v>-142.59489664</v>
       </c>
       <c r="Q86">
-        <v>-137.895897856</v>
+        <v>-139.62489664</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2050237375824597</v>
+        <v>0.2156386534212903</v>
       </c>
       <c r="T86">
-        <v>3.273807630582864</v>
+        <v>3.492061472621721</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.007221355157248211</v>
+        <v>0.007136398037751173</v>
       </c>
       <c r="W86">
-        <v>0.2340972044539209</v>
+        <v>0.2341172373426983</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.03008897982186753</v>
+        <v>0.02973499182396322</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2313454497544871</v>
+        <v>0.2332454497544871</v>
       </c>
       <c r="C87">
-        <v>-575.5669787723356</v>
+        <v>-586.0777083853743</v>
       </c>
       <c r="D87">
-        <v>85.11302122766433</v>
+        <v>84.2502916146256</v>
       </c>
       <c r="E87">
-        <v>-20.22000000000003</v>
+        <v>-10.572</v>
       </c>
       <c r="F87">
-        <v>820.0799999999999</v>
+        <v>829.728</v>
       </c>
       <c r="G87">
         <v>159.4</v>
@@ -8421,37 +8421,37 @@
         <v>5.75</v>
       </c>
       <c r="M87">
-        <v>193.374864</v>
+        <v>195.6498624</v>
       </c>
       <c r="N87">
-        <v>-187.624864</v>
+        <v>-189.8998624</v>
       </c>
       <c r="O87">
-        <v>-45.02996736</v>
+        <v>-45.575966976</v>
       </c>
       <c r="P87">
-        <v>-142.59489664</v>
+        <v>-144.323895424</v>
       </c>
       <c r="Q87">
-        <v>-139.62489664</v>
+        <v>-141.353895424</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2156386534212903</v>
+        <v>0.2277699858085254</v>
       </c>
       <c r="T87">
-        <v>3.492061472621721</v>
+        <v>3.741494434951844</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.007136398037751173</v>
+        <v>0.007053416665219183</v>
       </c>
       <c r="W87">
-        <v>0.2341172373426983</v>
+        <v>0.2341368043503413</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.02973499182396322</v>
+        <v>0.02938923610507993</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2332454497544871</v>
+        <v>0.2351454497544871</v>
       </c>
       <c r="C88">
-        <v>-586.0777083853743</v>
+        <v>-596.5711237585737</v>
       </c>
       <c r="D88">
-        <v>84.2502916146256</v>
+        <v>83.40487624142631</v>
       </c>
       <c r="E88">
-        <v>-10.572</v>
+        <v>-0.9239999999999782</v>
       </c>
       <c r="F88">
-        <v>829.728</v>
+        <v>839.376</v>
       </c>
       <c r="G88">
         <v>159.4</v>
@@ -8503,37 +8503,37 @@
         <v>5.75</v>
       </c>
       <c r="M88">
-        <v>195.6498624</v>
+        <v>197.9248608</v>
       </c>
       <c r="N88">
-        <v>-189.8998624</v>
+        <v>-192.1748608</v>
       </c>
       <c r="O88">
-        <v>-45.575966976</v>
+        <v>-46.121966592</v>
       </c>
       <c r="P88">
-        <v>-144.323895424</v>
+        <v>-146.052894208</v>
       </c>
       <c r="Q88">
-        <v>-141.353895424</v>
+        <v>-143.082894208</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2277699858085254</v>
+        <v>0.2417676770245658</v>
       </c>
       <c r="T88">
-        <v>3.741494434951844</v>
+        <v>4.029301699178909</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.007053416665219183</v>
+        <v>0.006972342910446548</v>
       </c>
       <c r="W88">
-        <v>0.2341368043503413</v>
+        <v>0.2341559215417167</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.02938923610507993</v>
+        <v>0.02905142879352729</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2351454497544871</v>
+        <v>0.2370454497544871</v>
       </c>
       <c r="C89">
-        <v>-596.5711237585737</v>
+        <v>-607.0477409364577</v>
       </c>
       <c r="D89">
-        <v>83.40487624142631</v>
+        <v>82.5762590635423</v>
       </c>
       <c r="E89">
-        <v>-0.9239999999999782</v>
+        <v>8.724000000000046</v>
       </c>
       <c r="F89">
-        <v>839.376</v>
+        <v>849.024</v>
       </c>
       <c r="G89">
         <v>159.4</v>
@@ -8585,37 +8585,37 @@
         <v>5.75</v>
       </c>
       <c r="M89">
-        <v>197.9248608</v>
+        <v>200.1998592</v>
       </c>
       <c r="N89">
-        <v>-192.1748608</v>
+        <v>-194.4498592</v>
       </c>
       <c r="O89">
-        <v>-46.121966592</v>
+        <v>-46.667966208</v>
       </c>
       <c r="P89">
-        <v>-146.052894208</v>
+        <v>-147.781892992</v>
       </c>
       <c r="Q89">
-        <v>-143.082894208</v>
+        <v>-144.811892992</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2417676770245658</v>
+        <v>0.258098316776613</v>
       </c>
       <c r="T89">
-        <v>4.029301699178909</v>
+        <v>4.365076840777153</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.006972342910446548</v>
+        <v>0.006893111741009655</v>
       </c>
       <c r="W89">
-        <v>0.2341559215417167</v>
+        <v>0.2341746042514699</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.02905142879352729</v>
+        <v>0.02872129892087361</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2370454497544871</v>
+        <v>0.2389454497544871</v>
       </c>
       <c r="C90">
-        <v>-607.0477409364577</v>
+        <v>-617.5080556579288</v>
       </c>
       <c r="D90">
-        <v>82.5762590635423</v>
+        <v>81.76394434207123</v>
       </c>
       <c r="E90">
-        <v>8.724000000000046</v>
+        <v>18.37200000000007</v>
       </c>
       <c r="F90">
-        <v>849.024</v>
+        <v>858.672</v>
       </c>
       <c r="G90">
         <v>159.4</v>
@@ -8667,37 +8667,37 @@
         <v>5.75</v>
       </c>
       <c r="M90">
-        <v>200.1998592</v>
+        <v>202.4748576</v>
       </c>
       <c r="N90">
-        <v>-194.4498592</v>
+        <v>-196.7248576</v>
       </c>
       <c r="O90">
-        <v>-46.667966208</v>
+        <v>-47.213965824</v>
       </c>
       <c r="P90">
-        <v>-147.781892992</v>
+        <v>-149.510891776</v>
       </c>
       <c r="Q90">
-        <v>-144.811892992</v>
+        <v>-146.540891776</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.258098316776613</v>
+        <v>0.277398163756305</v>
       </c>
       <c r="T90">
-        <v>4.365076840777153</v>
+        <v>4.76190200812053</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.006893111741009655</v>
+        <v>0.006815661047290447</v>
       </c>
       <c r="W90">
-        <v>0.2341746042514699</v>
+        <v>0.2341928671250489</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.02872129892087361</v>
+        <v>0.02839858769704351</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2389454497544871</v>
+        <v>0.2408454497544871</v>
       </c>
       <c r="C91">
-        <v>-617.5080556579288</v>
+        <v>-627.9525443452858</v>
       </c>
       <c r="D91">
-        <v>81.76394434207123</v>
+        <v>80.96745565471407</v>
       </c>
       <c r="E91">
-        <v>18.37200000000007</v>
+        <v>28.01999999999998</v>
       </c>
       <c r="F91">
-        <v>858.672</v>
+        <v>868.3199999999999</v>
       </c>
       <c r="G91">
         <v>159.4</v>
@@ -8749,37 +8749,37 @@
         <v>5.75</v>
       </c>
       <c r="M91">
-        <v>202.4748576</v>
+        <v>204.749856</v>
       </c>
       <c r="N91">
-        <v>-196.7248576</v>
+        <v>-198.999856</v>
       </c>
       <c r="O91">
-        <v>-47.213965824</v>
+        <v>-47.75996543999999</v>
       </c>
       <c r="P91">
-        <v>-149.510891776</v>
+        <v>-151.23989056</v>
       </c>
       <c r="Q91">
-        <v>-146.540891776</v>
+        <v>-148.26989056</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.277398163756305</v>
+        <v>0.3005579801319356</v>
       </c>
       <c r="T91">
-        <v>4.76190200812053</v>
+        <v>5.238092208932583</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.006815661047290447</v>
+        <v>0.00673993148009833</v>
       </c>
       <c r="W91">
-        <v>0.2341928671250489</v>
+        <v>0.2342107241569928</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.02839858769704351</v>
+        <v>0.02808304783374305</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2408454497544871</v>
+        <v>0.2427454497544871</v>
       </c>
       <c r="C92">
-        <v>-627.9525443452858</v>
+        <v>-638.3816650359936</v>
       </c>
       <c r="D92">
-        <v>80.96745565471407</v>
+        <v>80.18633496400641</v>
       </c>
       <c r="E92">
-        <v>28.01999999999998</v>
+        <v>37.66800000000001</v>
       </c>
       <c r="F92">
-        <v>868.3199999999999</v>
+        <v>877.968</v>
       </c>
       <c r="G92">
         <v>159.4</v>
@@ -8831,37 +8831,37 @@
         <v>5.75</v>
       </c>
       <c r="M92">
-        <v>204.749856</v>
+        <v>207.0248544</v>
       </c>
       <c r="N92">
-        <v>-198.999856</v>
+        <v>-201.2748544</v>
       </c>
       <c r="O92">
-        <v>-47.75996543999999</v>
+        <v>-48.305965056</v>
       </c>
       <c r="P92">
-        <v>-151.23989056</v>
+        <v>-152.968889344</v>
       </c>
       <c r="Q92">
-        <v>-148.26989056</v>
+        <v>-149.998889344</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3005579801319356</v>
+        <v>0.3288644223688174</v>
       </c>
       <c r="T92">
-        <v>5.238092208932583</v>
+        <v>5.820102454369538</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.00673993148009833</v>
+        <v>0.006665866298998348</v>
       </c>
       <c r="W92">
-        <v>0.2342107241569928</v>
+        <v>0.2342281887266962</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.02808304783374305</v>
+        <v>0.02777444291249309</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2427454497544871</v>
+        <v>0.2446454497544871</v>
       </c>
       <c r="C93">
-        <v>-638.3816650359936</v>
+        <v>-648.795858261032</v>
       </c>
       <c r="D93">
-        <v>80.18633496400641</v>
+        <v>79.42014173896794</v>
       </c>
       <c r="E93">
-        <v>37.66800000000001</v>
+        <v>47.31600000000003</v>
       </c>
       <c r="F93">
-        <v>877.968</v>
+        <v>887.616</v>
       </c>
       <c r="G93">
         <v>159.4</v>
@@ -8913,37 +8913,37 @@
         <v>5.75</v>
       </c>
       <c r="M93">
-        <v>207.0248544</v>
+        <v>209.2998528</v>
       </c>
       <c r="N93">
-        <v>-201.2748544</v>
+        <v>-203.5498528</v>
       </c>
       <c r="O93">
-        <v>-48.305965056</v>
+        <v>-48.85196467199999</v>
       </c>
       <c r="P93">
-        <v>-152.968889344</v>
+        <v>-154.697888128</v>
       </c>
       <c r="Q93">
-        <v>-149.998889344</v>
+        <v>-151.727888128</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3288644223688174</v>
+        <v>0.3642474751649196</v>
       </c>
       <c r="T93">
-        <v>5.820102454369538</v>
+        <v>6.547615261165732</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.006665866298998348</v>
+        <v>0.006593411230530975</v>
       </c>
       <c r="W93">
-        <v>0.2342281887266962</v>
+        <v>0.2342452736318408</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.02777444291249309</v>
+        <v>0.02747254679387912</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2446454497544871</v>
+        <v>0.2465454497544871</v>
       </c>
       <c r="C94">
-        <v>-648.795858261032</v>
+        <v>-659.1955478733674</v>
       </c>
       <c r="D94">
-        <v>79.42014173896794</v>
+        <v>78.66845212663256</v>
       </c>
       <c r="E94">
-        <v>47.31600000000003</v>
+        <v>56.96400000000006</v>
       </c>
       <c r="F94">
-        <v>887.616</v>
+        <v>897.264</v>
       </c>
       <c r="G94">
         <v>159.4</v>
@@ -8995,37 +8995,37 @@
         <v>5.75</v>
       </c>
       <c r="M94">
-        <v>209.2998528</v>
+        <v>211.5748512</v>
       </c>
       <c r="N94">
-        <v>-203.5498528</v>
+        <v>-205.8248512</v>
       </c>
       <c r="O94">
-        <v>-48.85196467199999</v>
+        <v>-49.397964288</v>
       </c>
       <c r="P94">
-        <v>-154.697888128</v>
+        <v>-156.426886912</v>
       </c>
       <c r="Q94">
-        <v>-151.727888128</v>
+        <v>-153.456886912</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3642474751649196</v>
+        <v>0.4097399716170509</v>
       </c>
       <c r="T94">
-        <v>6.547615261165732</v>
+        <v>7.482988869903694</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.006593411230530975</v>
+        <v>0.006522514335579029</v>
       </c>
       <c r="W94">
-        <v>0.2342452736318408</v>
+        <v>0.2342619911196705</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.02747254679387912</v>
+        <v>0.02717714306491259</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2465454497544871</v>
+        <v>0.2484454497544871</v>
       </c>
       <c r="C95">
-        <v>-659.1955478733674</v>
+        <v>-669.5811418298156</v>
       </c>
       <c r="D95">
-        <v>78.66845212663256</v>
+        <v>77.93085817018452</v>
       </c>
       <c r="E95">
-        <v>56.96400000000006</v>
+        <v>66.61200000000008</v>
       </c>
       <c r="F95">
-        <v>897.264</v>
+        <v>906.912</v>
       </c>
       <c r="G95">
         <v>159.4</v>
@@ -9077,37 +9077,37 @@
         <v>5.75</v>
       </c>
       <c r="M95">
-        <v>211.5748512</v>
+        <v>213.8498496</v>
       </c>
       <c r="N95">
-        <v>-205.8248512</v>
+        <v>-208.0998496</v>
       </c>
       <c r="O95">
-        <v>-49.397964288</v>
+        <v>-49.94396390400001</v>
       </c>
       <c r="P95">
-        <v>-156.426886912</v>
+        <v>-158.155885696</v>
       </c>
       <c r="Q95">
-        <v>-153.456886912</v>
+        <v>-155.185885696</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4097399716170509</v>
+        <v>0.4703966335532263</v>
       </c>
       <c r="T95">
-        <v>7.482988869903694</v>
+        <v>8.730153681554313</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.006522514335579029</v>
+        <v>0.006453125885200528</v>
       </c>
       <c r="W95">
-        <v>0.2342619911196705</v>
+        <v>0.2342783529162697</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.02717714306491259</v>
+        <v>0.02688802452166883</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2484454497544871</v>
+        <v>0.2503454497544871</v>
       </c>
       <c r="C96">
-        <v>-669.5811418298156</v>
+        <v>-679.9530329293294</v>
       </c>
       <c r="D96">
-        <v>77.93085817018452</v>
+        <v>77.2069670706706</v>
       </c>
       <c r="E96">
-        <v>66.61200000000008</v>
+        <v>76.2600000000001</v>
       </c>
       <c r="F96">
-        <v>906.912</v>
+        <v>916.5600000000001</v>
       </c>
       <c r="G96">
         <v>159.4</v>
@@ -9159,37 +9159,37 @@
         <v>5.75</v>
       </c>
       <c r="M96">
-        <v>213.8498496</v>
+        <v>216.124848</v>
       </c>
       <c r="N96">
-        <v>-208.0998496</v>
+        <v>-210.374848</v>
       </c>
       <c r="O96">
-        <v>-49.94396390400001</v>
+        <v>-50.48996352</v>
       </c>
       <c r="P96">
-        <v>-158.155885696</v>
+        <v>-159.88488448</v>
       </c>
       <c r="Q96">
-        <v>-155.185885696</v>
+        <v>-156.91488448</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4703966335532263</v>
+        <v>0.5553159602638716</v>
       </c>
       <c r="T96">
-        <v>8.730153681554313</v>
+        <v>10.47618441786518</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.006453125885200528</v>
+        <v>0.00638519824430368</v>
       </c>
       <c r="W96">
-        <v>0.2342783529162697</v>
+        <v>0.2342943702539932</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.02688802452166883</v>
+        <v>0.02660499268459871</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2503454497544871</v>
+        <v>0.2522454497544871</v>
       </c>
       <c r="C97">
-        <v>-679.9530329293294</v>
+        <v>-690.3115995105195</v>
       </c>
       <c r="D97">
-        <v>77.2069670706706</v>
+        <v>76.49640048948059</v>
       </c>
       <c r="E97">
-        <v>76.2600000000001</v>
+        <v>85.90800000000013</v>
       </c>
       <c r="F97">
-        <v>916.5600000000001</v>
+        <v>926.2080000000001</v>
       </c>
       <c r="G97">
         <v>159.4</v>
@@ -9241,37 +9241,37 @@
         <v>5.75</v>
       </c>
       <c r="M97">
-        <v>216.124848</v>
+        <v>218.3998464</v>
       </c>
       <c r="N97">
-        <v>-210.374848</v>
+        <v>-212.6498464</v>
       </c>
       <c r="O97">
-        <v>-50.48996352</v>
+        <v>-51.03596313600001</v>
       </c>
       <c r="P97">
-        <v>-159.88488448</v>
+        <v>-161.613883264</v>
       </c>
       <c r="Q97">
-        <v>-156.91488448</v>
+        <v>-158.643883264</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5553159602638716</v>
+        <v>0.68269495032984</v>
       </c>
       <c r="T97">
-        <v>10.47618441786518</v>
+        <v>13.09523052233148</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.00638519824430368</v>
+        <v>0.006318685762592184</v>
       </c>
       <c r="W97">
-        <v>0.2342943702539932</v>
+        <v>0.2343100538971808</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.02660499268459871</v>
+        <v>0.02632785734413412</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.252245449754487</v>
+        <v>0.2541454497544871</v>
       </c>
       <c r="C98">
-        <v>-690.3115995105193</v>
+        <v>-700.6572061110055</v>
       </c>
       <c r="D98">
-        <v>76.49640048948068</v>
+        <v>75.79879388899437</v>
       </c>
       <c r="E98">
-        <v>85.90800000000002</v>
+        <v>95.55599999999993</v>
       </c>
       <c r="F98">
-        <v>926.208</v>
+        <v>935.8559999999999</v>
       </c>
       <c r="G98">
         <v>159.4</v>
@@ -9323,37 +9323,37 @@
         <v>5.75</v>
       </c>
       <c r="M98">
-        <v>218.3998464</v>
+        <v>220.6748448</v>
       </c>
       <c r="N98">
-        <v>-212.6498464</v>
+        <v>-214.9248448</v>
       </c>
       <c r="O98">
-        <v>-51.035963136</v>
+        <v>-51.581962752</v>
       </c>
       <c r="P98">
-        <v>-161.613883264</v>
+        <v>-163.342882048</v>
       </c>
       <c r="Q98">
-        <v>-158.643883264</v>
+        <v>-160.372882048</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6826949503298382</v>
+        <v>0.8949932671064511</v>
       </c>
       <c r="T98">
-        <v>13.09523052233144</v>
+        <v>17.4603073631086</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.006318685762592185</v>
+        <v>0.006253544672256183</v>
       </c>
       <c r="W98">
-        <v>0.2343100538971808</v>
+        <v>0.234325414166282</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.02632785734413412</v>
+        <v>0.02605643613440078</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2541454497544871</v>
+        <v>0.2560454497544871</v>
       </c>
       <c r="C99">
-        <v>-700.6572061110055</v>
+        <v>-710.9902040910201</v>
       </c>
       <c r="D99">
-        <v>75.79879388899437</v>
+        <v>75.1137959089797</v>
       </c>
       <c r="E99">
-        <v>95.55599999999993</v>
+        <v>105.204</v>
       </c>
       <c r="F99">
-        <v>935.8559999999999</v>
+        <v>945.5039999999999</v>
       </c>
       <c r="G99">
         <v>159.4</v>
@@ -9405,37 +9405,37 @@
         <v>5.75</v>
       </c>
       <c r="M99">
-        <v>220.6748448</v>
+        <v>222.9498432</v>
       </c>
       <c r="N99">
-        <v>-214.9248448</v>
+        <v>-217.1998432</v>
       </c>
       <c r="O99">
-        <v>-51.581962752</v>
+        <v>-52.12796236799999</v>
       </c>
       <c r="P99">
-        <v>-163.342882048</v>
+        <v>-165.071880832</v>
       </c>
       <c r="Q99">
-        <v>-160.372882048</v>
+        <v>-162.101880832</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.8949932671064511</v>
+        <v>1.319589900659677</v>
       </c>
       <c r="T99">
-        <v>17.4603073631086</v>
+        <v>26.19046104466289</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.006253544672256183</v>
+        <v>0.006189732991927039</v>
       </c>
       <c r="W99">
-        <v>0.234325414166282</v>
+        <v>0.2343404609605036</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.02605643613440078</v>
+        <v>0.02579055413302933</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2560454497544871</v>
+        <v>0.2579454497544871</v>
       </c>
       <c r="C100">
-        <v>-710.9902040910201</v>
+        <v>-721.3109322234982</v>
       </c>
       <c r="D100">
-        <v>75.1137959089797</v>
+        <v>74.44106777650167</v>
       </c>
       <c r="E100">
-        <v>105.204</v>
+        <v>114.852</v>
       </c>
       <c r="F100">
-        <v>945.5039999999999</v>
+        <v>955.1519999999999</v>
       </c>
       <c r="G100">
         <v>159.4</v>
@@ -9487,37 +9487,37 @@
         <v>5.75</v>
       </c>
       <c r="M100">
-        <v>222.9498432</v>
+        <v>225.2248416</v>
       </c>
       <c r="N100">
-        <v>-217.1998432</v>
+        <v>-219.4748416</v>
       </c>
       <c r="O100">
-        <v>-52.12796236799999</v>
+        <v>-52.67396198399999</v>
       </c>
       <c r="P100">
-        <v>-165.071880832</v>
+        <v>-166.800879616</v>
       </c>
       <c r="Q100">
-        <v>-162.101880832</v>
+        <v>-163.830879616</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.319589900659677</v>
+        <v>2.593379801319353</v>
       </c>
       <c r="T100">
-        <v>26.19046104466289</v>
+        <v>52.38092208932578</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.006189732991927039</v>
+        <v>0.006127210436453027</v>
       </c>
       <c r="W100">
-        <v>0.2343404609605036</v>
+        <v>0.2343552037790844</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.02579055413302933</v>
+        <v>0.02553004348522092</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2579454497544871</v>
-      </c>
-      <c r="C101">
-        <v>-721.3109322234982</v>
-      </c>
-      <c r="D101">
-        <v>74.44106777650167</v>
-      </c>
-      <c r="E101">
-        <v>114.852</v>
-      </c>
-      <c r="F101">
-        <v>955.1519999999999</v>
-      </c>
-      <c r="G101">
-        <v>159.4</v>
-      </c>
-      <c r="H101">
-        <v>124.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>8.720000000000001</v>
-      </c>
-      <c r="K101">
-        <v>2.97</v>
-      </c>
-      <c r="L101">
-        <v>5.75</v>
-      </c>
-      <c r="M101">
-        <v>225.2248416</v>
-      </c>
-      <c r="N101">
-        <v>-219.4748416</v>
-      </c>
-      <c r="O101">
-        <v>-52.67396198399999</v>
-      </c>
-      <c r="P101">
-        <v>-166.800879616</v>
-      </c>
-      <c r="Q101">
-        <v>-163.830879616</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.593379801319353</v>
-      </c>
-      <c r="T101">
-        <v>52.38092208932578</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.006127210436453027</v>
-      </c>
-      <c r="W101">
-        <v>0.2343552037790844</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.02553004348522092</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
